--- a/doubleUp.xlsx
+++ b/doubleUp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\letenok.DWA\Documents\streaks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5EB800F-F36D-4026-BC3E-D2D2AE23EF41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763F6F65-DA9F-4AF1-8FC1-3859915224EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="12" xr2:uid="{AC0F40C5-DAD0-4090-81D9-C61109D09DEF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="13" xr2:uid="{AC0F40C5-DAD0-4090-81D9-C61109D09DEF}"/>
   </bookViews>
   <sheets>
     <sheet name="DoubleUpV1" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,9 @@
     <sheet name="SatSunFrame" sheetId="18" r:id="rId11"/>
     <sheet name="22 - 24 Nov" sheetId="19" r:id="rId12"/>
     <sheet name="Sheet2" sheetId="20" r:id="rId13"/>
+    <sheet name="Multipliers" sheetId="21" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="429">
   <si>
     <t>Mon</t>
   </si>
@@ -2083,6 +2083,84 @@
   </si>
   <si>
     <t>if KV mechelen scores for remainder of Season</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>R0,50*2</t>
+  </si>
+  <si>
+    <t>R0,25*4</t>
+  </si>
+  <si>
+    <t>R0,10*10</t>
+  </si>
+  <si>
+    <t>R0,05*20</t>
+  </si>
+  <si>
+    <t>R0,02*50</t>
+  </si>
+  <si>
+    <t>R0,01*100</t>
+  </si>
+  <si>
+    <t>R0,25*2</t>
+  </si>
+  <si>
+    <t>R0,10*5</t>
+  </si>
+  <si>
+    <t>R0,05*10</t>
+  </si>
+  <si>
+    <t>R0,02*25</t>
+  </si>
+  <si>
+    <t>R0,01*50</t>
+  </si>
+  <si>
+    <t>R0,10*2</t>
+  </si>
+  <si>
+    <t>R0,05*5</t>
+  </si>
+  <si>
+    <t>R0,02*12</t>
+  </si>
+  <si>
+    <t>R0,01*25</t>
+  </si>
+  <si>
+    <t>R0,05*2</t>
+  </si>
+  <si>
+    <t>R0,02*5</t>
+  </si>
+  <si>
+    <t>R0,01*10</t>
+  </si>
+  <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>DM1</t>
+  </si>
+  <si>
+    <t>DM2</t>
+  </si>
+  <si>
+    <t>DM3</t>
+  </si>
+  <si>
+    <t>DM4</t>
+  </si>
+  <si>
+    <t>DM5</t>
+  </si>
+  <si>
+    <t>DM6</t>
   </si>
 </sst>
 </file>
@@ -2478,7 +2556,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -2701,11 +2779,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -2947,6 +3056,24 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2955,12 +3082,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2988,6 +3109,12 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3052,6 +3179,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3528,16 +3657,16 @@
       <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="147">
+      <c r="B8" s="153">
         <v>45</v>
       </c>
-      <c r="C8" s="147"/>
-      <c r="D8" s="147"/>
-      <c r="E8" s="147"/>
-      <c r="F8" s="147"/>
-      <c r="G8" s="147"/>
-      <c r="H8" s="147"/>
-      <c r="I8" s="147"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
+      <c r="I8" s="153"/>
       <c r="J8">
         <f>45+45</f>
         <v>90</v>
@@ -3602,7 +3731,11 @@
         <v>5760</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>403</v>
+      </c>
+    </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
@@ -3627,10 +3760,10 @@
     <row r="13" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:20" s="10" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="148" t="s">
+      <c r="A15" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="149">
+      <c r="B15" s="155">
         <v>1000</v>
       </c>
       <c r="C15" s="12" t="s">
@@ -3641,8 +3774,8 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="148"/>
-      <c r="B16" s="149"/>
+      <c r="A16" s="154"/>
+      <c r="B16" s="155"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -3717,7 +3850,7 @@
     <row r="29" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="30" spans="1:9" s="14" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="148" t="s">
+      <c r="A31" s="154" t="s">
         <v>17</v>
       </c>
       <c r="B31" t="s">
@@ -3731,34 +3864,34 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="148"/>
+      <c r="A32" s="154"/>
       <c r="B32" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="148"/>
+      <c r="A33" s="154"/>
       <c r="B33" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="148"/>
+      <c r="A34" s="154"/>
       <c r="B34" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="148"/>
+      <c r="A35" s="154"/>
       <c r="B35" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="148"/>
+      <c r="A36" s="154"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="148"/>
+      <c r="A37" s="154"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -3879,10 +4012,10 @@
       <c r="X2" s="93"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="175" t="s">
+      <c r="A3" s="181" t="s">
         <v>278</v>
       </c>
-      <c r="B3" s="176"/>
+      <c r="B3" s="182"/>
       <c r="C3" t="s">
         <v>279</v>
       </c>
@@ -3911,8 +4044,8 @@
       <c r="X3" s="93"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="177"/>
-      <c r="B4" s="178"/>
+      <c r="A4" s="183"/>
+      <c r="B4" s="184"/>
       <c r="C4" t="s">
         <v>283</v>
       </c>
@@ -3941,8 +4074,8 @@
       <c r="X4" s="93"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="177"/>
-      <c r="B5" s="178"/>
+      <c r="A5" s="183"/>
+      <c r="B5" s="184"/>
       <c r="C5" t="s">
         <v>299</v>
       </c>
@@ -3971,8 +4104,8 @@
       <c r="X5" s="93"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="177"/>
-      <c r="B6" s="178"/>
+      <c r="A6" s="183"/>
+      <c r="B6" s="184"/>
       <c r="D6" s="91"/>
       <c r="E6" s="91"/>
       <c r="F6" s="91"/>
@@ -3996,8 +4129,8 @@
       <c r="X6" s="93"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" s="177"/>
-      <c r="B7" s="178"/>
+      <c r="A7" s="183"/>
+      <c r="B7" s="184"/>
       <c r="D7" s="91"/>
       <c r="E7" s="91"/>
       <c r="F7" s="91"/>
@@ -4021,8 +4154,8 @@
       <c r="X7" s="93"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="177"/>
-      <c r="B8" s="178"/>
+      <c r="A8" s="183"/>
+      <c r="B8" s="184"/>
       <c r="D8" s="91"/>
       <c r="E8" s="91"/>
       <c r="F8" s="91"/>
@@ -4046,8 +4179,8 @@
       <c r="X8" s="93"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="177"/>
-      <c r="B9" s="178"/>
+      <c r="A9" s="183"/>
+      <c r="B9" s="184"/>
       <c r="D9" s="91"/>
       <c r="E9" s="91"/>
       <c r="F9" s="91"/>
@@ -4071,8 +4204,8 @@
       <c r="X9" s="93"/>
     </row>
     <row r="10" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="179"/>
-      <c r="B10" s="180"/>
+      <c r="A10" s="185"/>
+      <c r="B10" s="186"/>
       <c r="D10" s="91"/>
       <c r="E10" s="91"/>
       <c r="F10" s="91"/>
@@ -4165,10 +4298,10 @@
       <c r="X13" s="93"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="148" t="s">
+      <c r="A14" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="148"/>
+      <c r="B14" s="154"/>
       <c r="C14" t="s">
         <v>271</v>
       </c>
@@ -4199,8 +4332,8 @@
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="148"/>
-      <c r="B15" s="148"/>
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
       <c r="C15" t="s">
         <v>301</v>
       </c>
@@ -4233,8 +4366,8 @@
       <c r="X15" s="93"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="148"/>
-      <c r="B16" s="148"/>
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
       <c r="C16" t="s">
         <v>275</v>
       </c>
@@ -4263,8 +4396,8 @@
       <c r="X16" s="93"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A17" s="148"/>
-      <c r="B17" s="148"/>
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
       <c r="C17" t="s">
         <v>276</v>
       </c>
@@ -4295,8 +4428,8 @@
       <c r="X17" s="93"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A18" s="148"/>
-      <c r="B18" s="148"/>
+      <c r="A18" s="154"/>
+      <c r="B18" s="154"/>
       <c r="C18" t="s">
         <v>280</v>
       </c>
@@ -4327,8 +4460,8 @@
       <c r="X18" s="93"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A19" s="148"/>
-      <c r="B19" s="148"/>
+      <c r="A19" s="154"/>
+      <c r="B19" s="154"/>
       <c r="C19" t="s">
         <v>282</v>
       </c>
@@ -4359,8 +4492,8 @@
       <c r="X19" s="93"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A20" s="148"/>
-      <c r="B20" s="148"/>
+      <c r="A20" s="154"/>
+      <c r="B20" s="154"/>
       <c r="C20" t="s">
         <v>285</v>
       </c>
@@ -4389,8 +4522,8 @@
       <c r="X20" s="93"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A21" s="148"/>
-      <c r="B21" s="148"/>
+      <c r="A21" s="154"/>
+      <c r="B21" s="154"/>
       <c r="C21" t="s">
         <v>287</v>
       </c>
@@ -4421,8 +4554,8 @@
       <c r="X21" s="93"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A22" s="148"/>
-      <c r="B22" s="148"/>
+      <c r="A22" s="154"/>
+      <c r="B22" s="154"/>
       <c r="C22" t="s">
         <v>298</v>
       </c>
@@ -4451,8 +4584,8 @@
       <c r="X22" s="93"/>
     </row>
     <row r="23" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="181"/>
-      <c r="B23" s="181"/>
+      <c r="A23" s="187"/>
+      <c r="B23" s="187"/>
       <c r="C23" t="s">
         <v>299</v>
       </c>
@@ -4596,10 +4729,10 @@
       <c r="X28" s="93"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="154" t="s">
         <v>252</v>
       </c>
-      <c r="B29" s="148"/>
+      <c r="B29" s="154"/>
       <c r="C29" t="s">
         <v>303</v>
       </c>
@@ -4628,8 +4761,8 @@
       <c r="X29" s="93"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A30" s="148"/>
-      <c r="B30" s="148"/>
+      <c r="A30" s="154"/>
+      <c r="B30" s="154"/>
       <c r="C30" t="s">
         <v>302</v>
       </c>
@@ -4658,8 +4791,8 @@
       <c r="X30" s="93"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A31" s="148"/>
-      <c r="B31" s="148"/>
+      <c r="A31" s="154"/>
+      <c r="B31" s="154"/>
       <c r="C31" t="s">
         <v>301</v>
       </c>
@@ -4688,8 +4821,8 @@
       <c r="X31" s="93"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A32" s="148"/>
-      <c r="B32" s="148"/>
+      <c r="A32" s="154"/>
+      <c r="B32" s="154"/>
       <c r="C32" t="s">
         <v>300</v>
       </c>
@@ -4718,8 +4851,8 @@
       <c r="X32" s="93"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A33" s="148"/>
-      <c r="B33" s="148"/>
+      <c r="A33" s="154"/>
+      <c r="B33" s="154"/>
       <c r="C33" t="s">
         <v>299</v>
       </c>
@@ -4750,8 +4883,8 @@
       <c r="X33" s="93"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A34" s="148"/>
-      <c r="B34" s="148"/>
+      <c r="A34" s="154"/>
+      <c r="B34" s="154"/>
       <c r="C34" t="s">
         <v>297</v>
       </c>
@@ -4782,8 +4915,8 @@
       <c r="X34" s="93"/>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A35" s="148"/>
-      <c r="B35" s="148"/>
+      <c r="A35" s="154"/>
+      <c r="B35" s="154"/>
       <c r="C35" t="s">
         <v>295</v>
       </c>
@@ -4812,8 +4945,8 @@
       <c r="X35" s="93"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A36" s="148"/>
-      <c r="B36" s="148"/>
+      <c r="A36" s="154"/>
+      <c r="B36" s="154"/>
       <c r="C36" t="s">
         <v>294</v>
       </c>
@@ -4842,8 +4975,8 @@
       <c r="X36" s="93"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A37" s="148"/>
-      <c r="B37" s="148"/>
+      <c r="A37" s="154"/>
+      <c r="B37" s="154"/>
       <c r="C37" t="s">
         <v>293</v>
       </c>
@@ -4872,8 +5005,8 @@
       <c r="X37" s="93"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A38" s="148"/>
-      <c r="B38" s="148"/>
+      <c r="A38" s="154"/>
+      <c r="B38" s="154"/>
       <c r="C38" t="s">
         <v>292</v>
       </c>
@@ -4906,8 +5039,8 @@
       <c r="X38" s="93"/>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A39" s="148"/>
-      <c r="B39" s="148"/>
+      <c r="A39" s="154"/>
+      <c r="B39" s="154"/>
       <c r="C39" t="s">
         <v>291</v>
       </c>
@@ -4936,8 +5069,8 @@
       <c r="X39" s="93"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A40" s="148"/>
-      <c r="B40" s="148"/>
+      <c r="A40" s="154"/>
+      <c r="B40" s="154"/>
       <c r="C40" t="s">
         <v>290</v>
       </c>
@@ -4968,8 +5101,8 @@
       <c r="X40" s="93"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A41" s="148"/>
-      <c r="B41" s="148"/>
+      <c r="A41" s="154"/>
+      <c r="B41" s="154"/>
       <c r="C41" t="s">
         <v>289</v>
       </c>
@@ -5000,8 +5133,8 @@
       <c r="X41" s="93"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A42" s="148"/>
-      <c r="B42" s="148"/>
+      <c r="A42" s="154"/>
+      <c r="B42" s="154"/>
       <c r="C42" t="s">
         <v>287</v>
       </c>
@@ -5034,8 +5167,8 @@
       <c r="X42" s="93"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A43" s="148"/>
-      <c r="B43" s="148"/>
+      <c r="A43" s="154"/>
+      <c r="B43" s="154"/>
       <c r="C43" t="s">
         <v>288</v>
       </c>
@@ -5066,8 +5199,8 @@
       <c r="X43" s="93"/>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A44" s="148"/>
-      <c r="B44" s="148"/>
+      <c r="A44" s="154"/>
+      <c r="B44" s="154"/>
       <c r="C44" t="s">
         <v>286</v>
       </c>
@@ -5096,8 +5229,8 @@
       <c r="X44" s="93"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A45" s="148"/>
-      <c r="B45" s="148"/>
+      <c r="A45" s="154"/>
+      <c r="B45" s="154"/>
       <c r="C45" t="s">
         <v>284</v>
       </c>
@@ -5126,8 +5259,8 @@
       <c r="X45" s="93"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A46" s="148"/>
-      <c r="B46" s="148"/>
+      <c r="A46" s="154"/>
+      <c r="B46" s="154"/>
       <c r="C46" t="s">
         <v>281</v>
       </c>
@@ -5156,8 +5289,8 @@
       <c r="X46" s="93"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A47" s="148"/>
-      <c r="B47" s="148"/>
+      <c r="A47" s="154"/>
+      <c r="B47" s="154"/>
       <c r="C47" t="s">
         <v>276</v>
       </c>
@@ -5188,8 +5321,8 @@
       <c r="X47" s="93"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A48" s="148"/>
-      <c r="B48" s="148"/>
+      <c r="A48" s="154"/>
+      <c r="B48" s="154"/>
       <c r="C48" t="s">
         <v>274</v>
       </c>
@@ -5218,8 +5351,8 @@
       <c r="X48" s="93"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A49" s="148"/>
-      <c r="B49" s="148"/>
+      <c r="A49" s="154"/>
+      <c r="B49" s="154"/>
       <c r="C49" t="s">
         <v>273</v>
       </c>
@@ -5248,8 +5381,8 @@
       <c r="X49" s="93"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A50" s="148"/>
-      <c r="B50" s="148"/>
+      <c r="A50" s="154"/>
+      <c r="B50" s="154"/>
       <c r="C50" t="s">
         <v>272</v>
       </c>
@@ -5278,8 +5411,8 @@
       <c r="X50" s="93"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A51" s="148"/>
-      <c r="B51" s="148"/>
+      <c r="A51" s="154"/>
+      <c r="B51" s="154"/>
       <c r="C51" t="s">
         <v>271</v>
       </c>
@@ -5312,8 +5445,8 @@
       </c>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A52" s="148"/>
-      <c r="B52" s="148"/>
+      <c r="A52" s="154"/>
+      <c r="B52" s="154"/>
       <c r="C52" t="s">
         <v>270</v>
       </c>
@@ -5344,8 +5477,8 @@
       <c r="X52" s="93"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A53" s="148"/>
-      <c r="B53" s="148"/>
+      <c r="A53" s="154"/>
+      <c r="B53" s="154"/>
       <c r="C53" t="s">
         <v>269</v>
       </c>
@@ -5376,8 +5509,8 @@
       <c r="X53" s="93"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A54" s="148"/>
-      <c r="B54" s="148"/>
+      <c r="A54" s="154"/>
+      <c r="B54" s="154"/>
       <c r="C54" t="s">
         <v>268</v>
       </c>
@@ -5405,8 +5538,8 @@
       <c r="X54" s="93"/>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A55" s="148"/>
-      <c r="B55" s="148"/>
+      <c r="A55" s="154"/>
+      <c r="B55" s="154"/>
       <c r="C55" t="s">
         <v>267</v>
       </c>
@@ -5435,8 +5568,8 @@
       <c r="X55" s="93"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A56" s="148"/>
-      <c r="B56" s="148"/>
+      <c r="A56" s="154"/>
+      <c r="B56" s="154"/>
       <c r="C56" t="s">
         <v>266</v>
       </c>
@@ -5469,8 +5602,8 @@
       <c r="X56" s="93"/>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A57" s="148"/>
-      <c r="B57" s="148"/>
+      <c r="A57" s="154"/>
+      <c r="B57" s="154"/>
       <c r="C57" t="s">
         <v>264</v>
       </c>
@@ -5499,8 +5632,8 @@
       <c r="X57" s="93"/>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A58" s="148"/>
-      <c r="B58" s="148"/>
+      <c r="A58" s="154"/>
+      <c r="B58" s="154"/>
       <c r="C58" t="s">
         <v>262</v>
       </c>
@@ -5529,8 +5662,8 @@
       <c r="X58" s="93"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A59" s="148"/>
-      <c r="B59" s="148"/>
+      <c r="A59" s="154"/>
+      <c r="B59" s="154"/>
       <c r="C59" t="s">
         <v>263</v>
       </c>
@@ -5559,8 +5692,8 @@
       <c r="X59" s="93"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A60" s="148"/>
-      <c r="B60" s="148"/>
+      <c r="A60" s="154"/>
+      <c r="B60" s="154"/>
       <c r="C60" t="s">
         <v>248</v>
       </c>
@@ -5589,8 +5722,8 @@
       <c r="X60" s="93"/>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A61" s="148"/>
-      <c r="B61" s="148"/>
+      <c r="A61" s="154"/>
+      <c r="B61" s="154"/>
       <c r="C61" s="92" t="s">
         <v>250</v>
       </c>
@@ -5614,8 +5747,8 @@
       <c r="X61" s="93"/>
     </row>
     <row r="62" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="181"/>
-      <c r="B62" s="181"/>
+      <c r="A62" s="187"/>
+      <c r="B62" s="187"/>
       <c r="C62" t="s">
         <v>251</v>
       </c>
@@ -5643,10 +5776,10 @@
       <c r="W62" s="91"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A63" s="175" t="s">
+      <c r="A63" s="181" t="s">
         <v>247</v>
       </c>
-      <c r="B63" s="176"/>
+      <c r="B63" s="182"/>
       <c r="C63" t="s">
         <v>261</v>
       </c>
@@ -5674,8 +5807,8 @@
       <c r="W63" s="91"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A64" s="177"/>
-      <c r="B64" s="178"/>
+      <c r="A64" s="183"/>
+      <c r="B64" s="184"/>
       <c r="C64" t="s">
         <v>259</v>
       </c>
@@ -5703,8 +5836,8 @@
       <c r="W64" s="91"/>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A65" s="177"/>
-      <c r="B65" s="178"/>
+      <c r="A65" s="183"/>
+      <c r="B65" s="184"/>
       <c r="C65" t="s">
         <v>262</v>
       </c>
@@ -5736,8 +5869,8 @@
       <c r="W65" s="91"/>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A66" s="177"/>
-      <c r="B66" s="178"/>
+      <c r="A66" s="183"/>
+      <c r="B66" s="184"/>
       <c r="C66" s="95" t="s">
         <v>249</v>
       </c>
@@ -5769,8 +5902,8 @@
       <c r="W66" s="91"/>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A67" s="177"/>
-      <c r="B67" s="178"/>
+      <c r="A67" s="183"/>
+      <c r="B67" s="184"/>
       <c r="C67" s="92" t="s">
         <v>248</v>
       </c>
@@ -5804,8 +5937,8 @@
       <c r="W67" s="91"/>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A68" s="177"/>
-      <c r="B68" s="178"/>
+      <c r="A68" s="183"/>
+      <c r="B68" s="184"/>
       <c r="C68" s="92" t="s">
         <v>250</v>
       </c>
@@ -5837,8 +5970,8 @@
       <c r="W68" s="91"/>
     </row>
     <row r="69" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="179"/>
-      <c r="B69" s="180"/>
+      <c r="A69" s="185"/>
+      <c r="B69" s="186"/>
       <c r="C69" s="92" t="s">
         <v>251</v>
       </c>
@@ -5870,10 +6003,10 @@
       <c r="W69" s="91"/>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A70" s="175" t="s">
+      <c r="A70" s="181" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="176"/>
+      <c r="B70" s="182"/>
       <c r="C70" s="89" t="s">
         <v>249</v>
       </c>
@@ -5903,8 +6036,8 @@
       <c r="W70" s="91"/>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A71" s="177"/>
-      <c r="B71" s="178"/>
+      <c r="A71" s="183"/>
+      <c r="B71" s="184"/>
       <c r="C71" s="92" t="s">
         <v>248</v>
       </c>
@@ -5938,8 +6071,8 @@
       <c r="W71" s="91"/>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A72" s="177"/>
-      <c r="B72" s="178"/>
+      <c r="A72" s="183"/>
+      <c r="B72" s="184"/>
       <c r="C72" s="92" t="s">
         <v>250</v>
       </c>
@@ -5969,8 +6102,8 @@
       <c r="W72" s="91"/>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A73" s="177"/>
-      <c r="B73" s="178"/>
+      <c r="A73" s="183"/>
+      <c r="B73" s="184"/>
       <c r="C73" s="92" t="s">
         <v>251</v>
       </c>
@@ -6002,8 +6135,8 @@
       <c r="W73" s="91"/>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A74" s="177"/>
-      <c r="B74" s="178"/>
+      <c r="A74" s="183"/>
+      <c r="B74" s="184"/>
       <c r="C74" t="s">
         <v>261</v>
       </c>
@@ -6033,8 +6166,8 @@
       <c r="W74" s="91"/>
     </row>
     <row r="75" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="179"/>
-      <c r="B75" s="180"/>
+      <c r="A75" s="185"/>
+      <c r="B75" s="186"/>
       <c r="C75" t="s">
         <v>259</v>
       </c>
@@ -6062,10 +6195,10 @@
       <c r="W75" s="91"/>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A76" s="175" t="s">
+      <c r="A76" s="181" t="s">
         <v>255</v>
       </c>
-      <c r="B76" s="176"/>
+      <c r="B76" s="182"/>
       <c r="C76" s="92" t="s">
         <v>248</v>
       </c>
@@ -6093,8 +6226,8 @@
       <c r="W76" s="91"/>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A77" s="177"/>
-      <c r="B77" s="178"/>
+      <c r="A77" s="183"/>
+      <c r="B77" s="184"/>
       <c r="C77" s="89" t="s">
         <v>249</v>
       </c>
@@ -6122,8 +6255,8 @@
       <c r="W77" s="91"/>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A78" s="177"/>
-      <c r="B78" s="178"/>
+      <c r="A78" s="183"/>
+      <c r="B78" s="184"/>
       <c r="D78" s="91"/>
       <c r="E78" s="91"/>
       <c r="F78" s="91"/>
@@ -6146,8 +6279,8 @@
       <c r="W78" s="91"/>
     </row>
     <row r="79" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="179"/>
-      <c r="B79" s="180"/>
+      <c r="A79" s="185"/>
+      <c r="B79" s="186"/>
       <c r="D79" s="91"/>
       <c r="E79" s="91"/>
       <c r="F79" s="91"/>
@@ -6355,10 +6488,10 @@
       <c r="X2" s="93"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="175" t="s">
+      <c r="A3" s="181" t="s">
         <v>247</v>
       </c>
-      <c r="B3" s="176"/>
+      <c r="B3" s="182"/>
       <c r="C3" t="s">
         <v>261</v>
       </c>
@@ -6386,8 +6519,8 @@
       <c r="W3" s="91"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="177"/>
-      <c r="B4" s="178"/>
+      <c r="A4" s="183"/>
+      <c r="B4" s="184"/>
       <c r="C4" t="s">
         <v>259</v>
       </c>
@@ -6415,8 +6548,8 @@
       <c r="W4" s="91"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="177"/>
-      <c r="B5" s="178"/>
+      <c r="A5" s="183"/>
+      <c r="B5" s="184"/>
       <c r="C5" t="s">
         <v>262</v>
       </c>
@@ -6448,8 +6581,8 @@
       <c r="W5" s="91"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="177"/>
-      <c r="B6" s="178"/>
+      <c r="A6" s="183"/>
+      <c r="B6" s="184"/>
       <c r="C6" s="95" t="s">
         <v>249</v>
       </c>
@@ -6481,8 +6614,8 @@
       <c r="W6" s="91"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" s="177"/>
-      <c r="B7" s="178"/>
+      <c r="A7" s="183"/>
+      <c r="B7" s="184"/>
       <c r="C7" s="92" t="s">
         <v>248</v>
       </c>
@@ -6516,8 +6649,8 @@
       <c r="W7" s="91"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="177"/>
-      <c r="B8" s="178"/>
+      <c r="A8" s="183"/>
+      <c r="B8" s="184"/>
       <c r="C8" s="92" t="s">
         <v>250</v>
       </c>
@@ -6549,8 +6682,8 @@
       <c r="W8" s="91"/>
     </row>
     <row r="9" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="179"/>
-      <c r="B9" s="180"/>
+      <c r="A9" s="185"/>
+      <c r="B9" s="186"/>
       <c r="C9" s="92" t="s">
         <v>251</v>
       </c>
@@ -6582,10 +6715,10 @@
       <c r="W9" s="91"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="175" t="s">
+      <c r="A10" s="181" t="s">
         <v>254</v>
       </c>
-      <c r="B10" s="176"/>
+      <c r="B10" s="182"/>
       <c r="C10" s="89" t="s">
         <v>249</v>
       </c>
@@ -6615,8 +6748,8 @@
       <c r="W10" s="91"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="177"/>
-      <c r="B11" s="178"/>
+      <c r="A11" s="183"/>
+      <c r="B11" s="184"/>
       <c r="C11" s="92" t="s">
         <v>248</v>
       </c>
@@ -6650,8 +6783,8 @@
       <c r="W11" s="91"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="177"/>
-      <c r="B12" s="178"/>
+      <c r="A12" s="183"/>
+      <c r="B12" s="184"/>
       <c r="C12" s="92" t="s">
         <v>250</v>
       </c>
@@ -6681,8 +6814,8 @@
       <c r="W12" s="91"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="177"/>
-      <c r="B13" s="178"/>
+      <c r="A13" s="183"/>
+      <c r="B13" s="184"/>
       <c r="C13" s="92" t="s">
         <v>251</v>
       </c>
@@ -6714,8 +6847,8 @@
       <c r="W13" s="91"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="177"/>
-      <c r="B14" s="178"/>
+      <c r="A14" s="183"/>
+      <c r="B14" s="184"/>
       <c r="C14" t="s">
         <v>261</v>
       </c>
@@ -6745,8 +6878,8 @@
       <c r="W14" s="91"/>
     </row>
     <row r="15" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="179"/>
-      <c r="B15" s="180"/>
+      <c r="A15" s="185"/>
+      <c r="B15" s="186"/>
       <c r="C15" t="s">
         <v>259</v>
       </c>
@@ -7173,8 +7306,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="147"/>
-      <c r="B2" s="147"/>
+      <c r="A2" s="153"/>
+      <c r="B2" s="153"/>
       <c r="C2" t="s">
         <v>400</v>
       </c>
@@ -7191,10 +7324,10 @@
       <c r="L2" s="75"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="148" t="s">
+      <c r="A3" s="154" t="s">
         <v>252</v>
       </c>
-      <c r="B3" s="148"/>
+      <c r="B3" s="154"/>
       <c r="C3" t="s">
         <v>378</v>
       </c>
@@ -7203,8 +7336,8 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="148"/>
-      <c r="B4" s="148"/>
+      <c r="A4" s="154"/>
+      <c r="B4" s="154"/>
       <c r="C4" t="s">
         <v>379</v>
       </c>
@@ -7214,8 +7347,8 @@
       <c r="M4" s="125"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="148"/>
-      <c r="B5" s="148"/>
+      <c r="A5" s="154"/>
+      <c r="B5" s="154"/>
       <c r="C5" t="s">
         <v>339</v>
       </c>
@@ -7225,8 +7358,8 @@
       <c r="M5" s="125"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="148"/>
-      <c r="B6" s="148"/>
+      <c r="A6" s="154"/>
+      <c r="B6" s="154"/>
       <c r="C6" t="s">
         <v>380</v>
       </c>
@@ -7236,8 +7369,8 @@
       <c r="M6" s="125"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="148"/>
-      <c r="B7" s="148"/>
+      <c r="A7" s="154"/>
+      <c r="B7" s="154"/>
       <c r="C7" t="s">
         <v>381</v>
       </c>
@@ -7247,8 +7380,8 @@
       <c r="M7" s="125"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="148"/>
-      <c r="B8" s="148"/>
+      <c r="A8" s="154"/>
+      <c r="B8" s="154"/>
       <c r="C8" t="s">
         <v>382</v>
       </c>
@@ -7258,8 +7391,8 @@
       <c r="M8" s="125"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="148"/>
-      <c r="B9" s="148"/>
+      <c r="A9" s="154"/>
+      <c r="B9" s="154"/>
       <c r="C9" t="s">
         <v>334</v>
       </c>
@@ -7269,8 +7402,8 @@
       <c r="M9" s="125"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="148"/>
-      <c r="B10" s="148"/>
+      <c r="A10" s="154"/>
+      <c r="B10" s="154"/>
       <c r="C10" t="s">
         <v>340</v>
       </c>
@@ -7283,8 +7416,8 @@
       <c r="M10" s="125"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="148"/>
-      <c r="B11" s="148"/>
+      <c r="A11" s="154"/>
+      <c r="B11" s="154"/>
       <c r="C11" t="s">
         <v>383</v>
       </c>
@@ -7294,8 +7427,8 @@
       <c r="M11" s="125"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="148"/>
-      <c r="B12" s="148"/>
+      <c r="A12" s="154"/>
+      <c r="B12" s="154"/>
       <c r="C12" t="s">
         <v>384</v>
       </c>
@@ -7305,8 +7438,8 @@
       <c r="M12" s="125"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="148"/>
-      <c r="B13" s="148"/>
+      <c r="A13" s="154"/>
+      <c r="B13" s="154"/>
       <c r="C13" t="s">
         <v>335</v>
       </c>
@@ -7316,8 +7449,8 @@
       <c r="M13" s="125"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="148"/>
-      <c r="B14" s="148"/>
+      <c r="A14" s="154"/>
+      <c r="B14" s="154"/>
       <c r="C14" t="s">
         <v>330</v>
       </c>
@@ -7330,8 +7463,8 @@
       <c r="M14" s="125"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="148"/>
-      <c r="B15" s="148"/>
+      <c r="A15" s="154"/>
+      <c r="B15" s="154"/>
       <c r="C15" t="s">
         <v>331</v>
       </c>
@@ -7341,8 +7474,8 @@
       <c r="M15" s="125"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="148"/>
-      <c r="B16" s="148"/>
+      <c r="A16" s="154"/>
+      <c r="B16" s="154"/>
       <c r="C16" t="s">
         <v>344</v>
       </c>
@@ -7352,8 +7485,8 @@
       <c r="M16" s="125"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A17" s="148"/>
-      <c r="B17" s="148"/>
+      <c r="A17" s="154"/>
+      <c r="B17" s="154"/>
       <c r="C17" t="s">
         <v>385</v>
       </c>
@@ -7363,8 +7496,8 @@
       <c r="M17" s="125"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A18" s="148"/>
-      <c r="B18" s="148"/>
+      <c r="A18" s="154"/>
+      <c r="B18" s="154"/>
       <c r="C18" t="s">
         <v>386</v>
       </c>
@@ -7374,8 +7507,8 @@
       <c r="M18" s="125"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A19" s="148"/>
-      <c r="B19" s="148"/>
+      <c r="A19" s="154"/>
+      <c r="B19" s="154"/>
       <c r="C19" t="s">
         <v>387</v>
       </c>
@@ -7388,8 +7521,8 @@
       <c r="M19" s="125"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A20" s="148"/>
-      <c r="B20" s="148"/>
+      <c r="A20" s="154"/>
+      <c r="B20" s="154"/>
       <c r="C20" t="s">
         <v>388</v>
       </c>
@@ -7402,8 +7535,8 @@
       <c r="M20" s="125"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A21" s="148"/>
-      <c r="B21" s="148"/>
+      <c r="A21" s="154"/>
+      <c r="B21" s="154"/>
       <c r="C21" t="s">
         <v>389</v>
       </c>
@@ -7416,8 +7549,8 @@
       <c r="M21" s="125"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A22" s="148"/>
-      <c r="B22" s="148"/>
+      <c r="A22" s="154"/>
+      <c r="B22" s="154"/>
       <c r="C22" t="s">
         <v>390</v>
       </c>
@@ -7433,8 +7566,8 @@
       <c r="M22" s="125"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A23" s="148"/>
-      <c r="B23" s="148"/>
+      <c r="A23" s="154"/>
+      <c r="B23" s="154"/>
       <c r="C23" t="s">
         <v>391</v>
       </c>
@@ -7444,8 +7577,8 @@
       <c r="M23" s="125"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A24" s="148"/>
-      <c r="B24" s="148"/>
+      <c r="A24" s="154"/>
+      <c r="B24" s="154"/>
       <c r="C24" t="s">
         <v>343</v>
       </c>
@@ -7455,8 +7588,8 @@
       <c r="M24" s="125"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A25" s="148"/>
-      <c r="B25" s="148"/>
+      <c r="A25" s="154"/>
+      <c r="B25" s="154"/>
       <c r="C25" t="s">
         <v>392</v>
       </c>
@@ -7469,8 +7602,8 @@
       <c r="M25" s="125"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A26" s="148"/>
-      <c r="B26" s="148"/>
+      <c r="A26" s="154"/>
+      <c r="B26" s="154"/>
       <c r="C26" t="s">
         <v>393</v>
       </c>
@@ -7480,8 +7613,8 @@
       <c r="M26" s="125"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A27" s="148"/>
-      <c r="B27" s="148"/>
+      <c r="A27" s="154"/>
+      <c r="B27" s="154"/>
       <c r="D27" s="125"/>
       <c r="E27" s="125"/>
       <c r="F27" s="125"/>
@@ -7493,8 +7626,8 @@
       <c r="M27" s="125"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A28" s="148"/>
-      <c r="B28" s="148"/>
+      <c r="A28" s="154"/>
+      <c r="B28" s="154"/>
       <c r="D28" s="125"/>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
@@ -7507,8 +7640,8 @@
       <c r="M28" s="125"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A29" s="148"/>
-      <c r="B29" s="148"/>
+      <c r="A29" s="154"/>
+      <c r="B29" s="154"/>
       <c r="D29" s="125"/>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
@@ -7521,8 +7654,8 @@
       <c r="M29" s="125"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A30" s="148"/>
-      <c r="B30" s="148"/>
+      <c r="A30" s="154"/>
+      <c r="B30" s="154"/>
       <c r="D30" s="125"/>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -7535,8 +7668,8 @@
       <c r="M30" s="125"/>
     </row>
     <row r="31" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="181"/>
-      <c r="B31" s="181"/>
+      <c r="A31" s="187"/>
+      <c r="B31" s="187"/>
       <c r="D31" s="75"/>
       <c r="E31" s="75"/>
       <c r="F31" s="75"/>
@@ -7548,10 +7681,10 @@
       <c r="L31" s="75"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A32" s="175" t="s">
+      <c r="A32" s="181" t="s">
         <v>247</v>
       </c>
-      <c r="B32" s="176"/>
+      <c r="B32" s="182"/>
       <c r="C32" s="3" t="s">
         <v>264</v>
       </c>
@@ -7585,8 +7718,8 @@
       <c r="Y32" s="91"/>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A33" s="177"/>
-      <c r="B33" s="178"/>
+      <c r="A33" s="183"/>
+      <c r="B33" s="184"/>
       <c r="C33" t="s">
         <v>259</v>
       </c>
@@ -7616,8 +7749,8 @@
       <c r="Y33" s="91"/>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A34" s="177"/>
-      <c r="B34" s="178"/>
+      <c r="A34" s="183"/>
+      <c r="B34" s="184"/>
       <c r="C34" s="14" t="s">
         <v>262</v>
       </c>
@@ -7651,8 +7784,8 @@
       <c r="Y34" s="91"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A35" s="177"/>
-      <c r="B35" s="178"/>
+      <c r="A35" s="183"/>
+      <c r="B35" s="184"/>
       <c r="C35" s="100" t="s">
         <v>249</v>
       </c>
@@ -7686,8 +7819,8 @@
       <c r="Y35" s="91"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A36" s="177"/>
-      <c r="B36" s="178"/>
+      <c r="A36" s="183"/>
+      <c r="B36" s="184"/>
       <c r="C36" s="102" t="s">
         <v>248</v>
       </c>
@@ -7723,8 +7856,8 @@
       <c r="Y36" s="91"/>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A37" s="177"/>
-      <c r="B37" s="178"/>
+      <c r="A37" s="183"/>
+      <c r="B37" s="184"/>
       <c r="C37" s="101" t="s">
         <v>250</v>
       </c>
@@ -7756,8 +7889,8 @@
       <c r="Y37" s="91"/>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A38" s="177"/>
-      <c r="B38" s="178"/>
+      <c r="A38" s="183"/>
+      <c r="B38" s="184"/>
       <c r="C38" s="134" t="s">
         <v>340</v>
       </c>
@@ -7789,8 +7922,8 @@
       <c r="Y38" s="91"/>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A39" s="177"/>
-      <c r="B39" s="178"/>
+      <c r="A39" s="183"/>
+      <c r="B39" s="184"/>
       <c r="C39" s="36" t="s">
         <v>328</v>
       </c>
@@ -7811,8 +7944,8 @@
       <c r="L39" s="123"/>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A40" s="177"/>
-      <c r="B40" s="178"/>
+      <c r="A40" s="183"/>
+      <c r="B40" s="184"/>
       <c r="C40" s="103" t="s">
         <v>329</v>
       </c>
@@ -7835,8 +7968,8 @@
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A41" s="177"/>
-      <c r="B41" s="178"/>
+      <c r="A41" s="183"/>
+      <c r="B41" s="184"/>
       <c r="C41" s="3" t="s">
         <v>341</v>
       </c>
@@ -7853,8 +7986,8 @@
       <c r="L41" s="123"/>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A42" s="177"/>
-      <c r="B42" s="178"/>
+      <c r="A42" s="183"/>
+      <c r="B42" s="184"/>
       <c r="C42" s="19" t="s">
         <v>345</v>
       </c>
@@ -7875,8 +8008,8 @@
       <c r="L42" s="123"/>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A43" s="177"/>
-      <c r="B43" s="178"/>
+      <c r="A43" s="183"/>
+      <c r="B43" s="184"/>
       <c r="C43" s="104" t="s">
         <v>330</v>
       </c>
@@ -7895,8 +8028,8 @@
       <c r="L43" s="123"/>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A44" s="177"/>
-      <c r="B44" s="178"/>
+      <c r="A44" s="183"/>
+      <c r="B44" s="184"/>
       <c r="C44" s="105" t="s">
         <v>331</v>
       </c>
@@ -7915,8 +8048,8 @@
       <c r="L44" s="123"/>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A45" s="177"/>
-      <c r="B45" s="178"/>
+      <c r="A45" s="183"/>
+      <c r="B45" s="184"/>
       <c r="C45" s="14" t="s">
         <v>344</v>
       </c>
@@ -7941,8 +8074,8 @@
       <c r="L45" s="123"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A46" s="177"/>
-      <c r="B46" s="178"/>
+      <c r="A46" s="183"/>
+      <c r="B46" s="184"/>
       <c r="C46" s="106" t="s">
         <v>332</v>
       </c>
@@ -7959,8 +8092,8 @@
       <c r="L46" s="123"/>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A47" s="177"/>
-      <c r="B47" s="178"/>
+      <c r="A47" s="183"/>
+      <c r="B47" s="184"/>
       <c r="C47" s="19" t="s">
         <v>333</v>
       </c>
@@ -7979,8 +8112,8 @@
       <c r="L47" s="123"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A48" s="177"/>
-      <c r="B48" s="178"/>
+      <c r="A48" s="183"/>
+      <c r="B48" s="184"/>
       <c r="C48" s="10" t="s">
         <v>334</v>
       </c>
@@ -7999,8 +8132,8 @@
       <c r="L48" s="123"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A49" s="177"/>
-      <c r="B49" s="178"/>
+      <c r="A49" s="183"/>
+      <c r="B49" s="184"/>
       <c r="C49" s="2" t="s">
         <v>335</v>
       </c>
@@ -8019,8 +8152,8 @@
       <c r="L49" s="123"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A50" s="177"/>
-      <c r="B50" s="178"/>
+      <c r="A50" s="183"/>
+      <c r="B50" s="184"/>
       <c r="C50" s="107" t="s">
         <v>336</v>
       </c>
@@ -8041,8 +8174,8 @@
       <c r="L50" s="123"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A51" s="177"/>
-      <c r="B51" s="178"/>
+      <c r="A51" s="183"/>
+      <c r="B51" s="184"/>
       <c r="C51" s="3" t="s">
         <v>343</v>
       </c>
@@ -8063,8 +8196,8 @@
       <c r="L51" s="123"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" s="177"/>
-      <c r="B52" s="178"/>
+      <c r="A52" s="183"/>
+      <c r="B52" s="184"/>
       <c r="C52" s="131" t="s">
         <v>337</v>
       </c>
@@ -8085,8 +8218,8 @@
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" s="177"/>
-      <c r="B53" s="178"/>
+      <c r="A53" s="183"/>
+      <c r="B53" s="184"/>
       <c r="C53" s="108" t="s">
         <v>338</v>
       </c>
@@ -8107,8 +8240,8 @@
       <c r="L53" s="123"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" s="177"/>
-      <c r="B54" s="178"/>
+      <c r="A54" s="183"/>
+      <c r="B54" s="184"/>
       <c r="C54" s="105" t="s">
         <v>342</v>
       </c>
@@ -8125,8 +8258,8 @@
       <c r="L54" s="123"/>
     </row>
     <row r="55" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="179"/>
-      <c r="B55" s="180"/>
+      <c r="A55" s="185"/>
+      <c r="B55" s="186"/>
       <c r="C55" s="129" t="s">
         <v>339</v>
       </c>
@@ -9081,13 +9214,13 @@
       <c r="O121">
         <v>0.1</v>
       </c>
-      <c r="P121" s="147" t="s">
+      <c r="P121" s="153" t="s">
         <v>402</v>
       </c>
-      <c r="Q121" s="147"/>
-      <c r="R121" s="147"/>
-      <c r="S121" s="147"/>
-      <c r="T121" s="147"/>
+      <c r="Q121" s="153"/>
+      <c r="R121" s="153"/>
+      <c r="S121" s="153"/>
+      <c r="T121" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -9101,6 +9234,126 @@
     <oddHeader>&amp;C&amp;"Calibri"&amp;11&amp;K000000 SECRET&amp;1#_x000D_</oddHeader>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;11&amp;K000000 SECRET</oddFooter>
   </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA97A53A-C659-4557-BD63-A07E194BEEF6}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="8.88671875" style="140"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="147" t="s">
+        <v>422</v>
+      </c>
+      <c r="B1" s="148" t="s">
+        <v>423</v>
+      </c>
+      <c r="C1" s="149" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1" s="149" t="s">
+        <v>425</v>
+      </c>
+      <c r="E1" s="149" t="s">
+        <v>426</v>
+      </c>
+      <c r="F1" s="149" t="s">
+        <v>427</v>
+      </c>
+      <c r="G1" s="149" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="150">
+        <v>2</v>
+      </c>
+      <c r="B2" s="151" t="s">
+        <v>404</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="150">
+        <v>0.5</v>
+      </c>
+      <c r="B3" s="151" t="s">
+        <v>410</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="G3" s="21"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="150">
+        <v>0.25</v>
+      </c>
+      <c r="B4" s="151" t="s">
+        <v>415</v>
+      </c>
+      <c r="C4" s="152" t="s">
+        <v>416</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="150">
+        <v>0.1</v>
+      </c>
+      <c r="B5" s="151" t="s">
+        <v>419</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+    </row>
+    <row r="6" spans="1:7" s="188" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="189"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -9297,15 +9550,15 @@
       <c r="N5">
         <v>3</v>
       </c>
-      <c r="O5" s="151" t="s">
+      <c r="O5" s="166" t="s">
         <v>35</v>
       </c>
-      <c r="P5" s="151"/>
-      <c r="Q5" s="151"/>
-      <c r="R5" s="151"/>
-      <c r="S5" s="151"/>
-      <c r="T5" s="151"/>
-      <c r="U5" s="151"/>
+      <c r="P5" s="166"/>
+      <c r="Q5" s="166"/>
+      <c r="R5" s="166"/>
+      <c r="S5" s="166"/>
+      <c r="T5" s="166"/>
+      <c r="U5" s="166"/>
       <c r="V5" s="32"/>
       <c r="W5" s="32"/>
       <c r="Y5" s="29">
@@ -9357,13 +9610,13 @@
       <c r="N6">
         <v>4</v>
       </c>
-      <c r="O6" s="151"/>
-      <c r="P6" s="151"/>
-      <c r="Q6" s="151"/>
-      <c r="R6" s="151"/>
-      <c r="S6" s="151"/>
-      <c r="T6" s="151"/>
-      <c r="U6" s="151"/>
+      <c r="O6" s="166"/>
+      <c r="P6" s="166"/>
+      <c r="Q6" s="166"/>
+      <c r="R6" s="166"/>
+      <c r="S6" s="166"/>
+      <c r="T6" s="166"/>
+      <c r="U6" s="166"/>
       <c r="V6" s="32"/>
       <c r="W6" s="32"/>
       <c r="Y6">
@@ -9413,15 +9666,15 @@
       <c r="N7">
         <v>5</v>
       </c>
-      <c r="O7" s="151" t="s">
+      <c r="O7" s="166" t="s">
         <v>36</v>
       </c>
-      <c r="P7" s="151"/>
-      <c r="Q7" s="151"/>
-      <c r="R7" s="151"/>
-      <c r="S7" s="151"/>
-      <c r="T7" s="151"/>
-      <c r="U7" s="151"/>
+      <c r="P7" s="166"/>
+      <c r="Q7" s="166"/>
+      <c r="R7" s="166"/>
+      <c r="S7" s="166"/>
+      <c r="T7" s="166"/>
+      <c r="U7" s="166"/>
       <c r="V7" s="32"/>
       <c r="W7" s="32"/>
       <c r="Y7">
@@ -9470,13 +9723,13 @@
       <c r="N8">
         <v>6</v>
       </c>
-      <c r="O8" s="151"/>
-      <c r="P8" s="151"/>
-      <c r="Q8" s="151"/>
-      <c r="R8" s="151"/>
-      <c r="S8" s="151"/>
-      <c r="T8" s="151"/>
-      <c r="U8" s="151"/>
+      <c r="O8" s="166"/>
+      <c r="P8" s="166"/>
+      <c r="Q8" s="166"/>
+      <c r="R8" s="166"/>
+      <c r="S8" s="166"/>
+      <c r="T8" s="166"/>
+      <c r="U8" s="166"/>
       <c r="V8" s="32"/>
       <c r="W8" s="32"/>
       <c r="Y8">
@@ -9586,7 +9839,7 @@
         <f>130*0.3+130</f>
         <v>169</v>
       </c>
-      <c r="Q10" s="157">
+      <c r="Q10" s="161">
         <v>1</v>
       </c>
       <c r="Y10">
@@ -9640,8 +9893,8 @@
         <f>169*0.3+169</f>
         <v>219.7</v>
       </c>
-      <c r="Q11" s="157"/>
-      <c r="R11" s="158">
+      <c r="Q11" s="161"/>
+      <c r="R11" s="162">
         <v>2</v>
       </c>
       <c r="S11" s="35"/>
@@ -9659,9 +9912,9 @@
         <f>220*0.3+220</f>
         <v>286</v>
       </c>
-      <c r="Q12" s="157"/>
-      <c r="R12" s="158"/>
-      <c r="S12" s="159">
+      <c r="Q12" s="161"/>
+      <c r="R12" s="162"/>
+      <c r="S12" s="163">
         <v>4</v>
       </c>
       <c r="Y12">
@@ -9681,10 +9934,10 @@
         <f>286*0.3+286</f>
         <v>371.8</v>
       </c>
-      <c r="Q13" s="157"/>
-      <c r="R13" s="158"/>
-      <c r="S13" s="159"/>
-      <c r="T13" s="160">
+      <c r="Q13" s="161"/>
+      <c r="R13" s="162"/>
+      <c r="S13" s="163"/>
+      <c r="T13" s="164">
         <v>8</v>
       </c>
       <c r="Y13">
@@ -9693,10 +9946,10 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J14" s="155">
+      <c r="J14" s="159">
         <v>14</v>
       </c>
-      <c r="K14" s="155"/>
+      <c r="K14" s="159"/>
       <c r="M14" s="24"/>
       <c r="N14">
         <v>12</v>
@@ -9705,11 +9958,11 @@
         <f>372*0.3+372</f>
         <v>483.6</v>
       </c>
-      <c r="Q14" s="157"/>
-      <c r="R14" s="158"/>
-      <c r="S14" s="159"/>
-      <c r="T14" s="160"/>
-      <c r="U14" s="150">
+      <c r="Q14" s="161"/>
+      <c r="R14" s="162"/>
+      <c r="S14" s="163"/>
+      <c r="T14" s="164"/>
+      <c r="U14" s="165">
         <v>16</v>
       </c>
       <c r="Y14">
@@ -9718,11 +9971,11 @@
       </c>
     </row>
     <row r="15" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I15" s="155">
+      <c r="I15" s="159">
         <v>28</v>
       </c>
-      <c r="J15" s="155"/>
-      <c r="K15" s="155"/>
+      <c r="J15" s="159"/>
+      <c r="K15" s="159"/>
       <c r="M15" s="24"/>
       <c r="N15">
         <v>13</v>
@@ -9731,23 +9984,23 @@
         <f>484*0.3+484</f>
         <v>629.20000000000005</v>
       </c>
-      <c r="Q15" s="157"/>
-      <c r="R15" s="158"/>
-      <c r="S15" s="159"/>
-      <c r="T15" s="160"/>
-      <c r="U15" s="150"/>
+      <c r="Q15" s="161"/>
+      <c r="R15" s="162"/>
+      <c r="S15" s="163"/>
+      <c r="T15" s="164"/>
+      <c r="U15" s="165"/>
       <c r="Y15">
         <f>Y14*Z5+Y14</f>
         <v>179.21603940369999</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H16" s="155">
+      <c r="H16" s="159">
         <v>56</v>
       </c>
-      <c r="I16" s="155"/>
-      <c r="J16" s="155"/>
-      <c r="K16" s="155"/>
+      <c r="I16" s="159"/>
+      <c r="J16" s="159"/>
+      <c r="K16" s="159"/>
       <c r="M16" s="24"/>
       <c r="N16">
         <v>14</v>
@@ -9756,24 +10009,24 @@
         <f>630*0.3+630</f>
         <v>819</v>
       </c>
-      <c r="Q16" s="157"/>
-      <c r="R16" s="158"/>
-      <c r="S16" s="159"/>
-      <c r="T16" s="160"/>
-      <c r="U16" s="150"/>
+      <c r="Q16" s="161"/>
+      <c r="R16" s="162"/>
+      <c r="S16" s="163"/>
+      <c r="T16" s="164"/>
+      <c r="U16" s="165"/>
       <c r="Y16">
         <f>Y15*Z5+Y15</f>
         <v>232.98085122480998</v>
       </c>
     </row>
     <row r="17" spans="3:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G17" s="155">
+      <c r="G17" s="159">
         <v>106</v>
       </c>
-      <c r="H17" s="155"/>
-      <c r="I17" s="155"/>
-      <c r="J17" s="155"/>
-      <c r="K17" s="155"/>
+      <c r="H17" s="159"/>
+      <c r="I17" s="159"/>
+      <c r="J17" s="159"/>
+      <c r="K17" s="159"/>
       <c r="M17" s="24"/>
       <c r="N17">
         <v>15</v>
@@ -9782,25 +10035,25 @@
         <f>820*0.3+820</f>
         <v>1066</v>
       </c>
-      <c r="Q17" s="157"/>
-      <c r="R17" s="158"/>
-      <c r="S17" s="159"/>
-      <c r="T17" s="160"/>
-      <c r="U17" s="150"/>
+      <c r="Q17" s="161"/>
+      <c r="R17" s="162"/>
+      <c r="S17" s="163"/>
+      <c r="T17" s="164"/>
+      <c r="U17" s="165"/>
       <c r="Y17">
         <f>Y16*Z5+Y16</f>
         <v>302.87510659225296</v>
       </c>
     </row>
     <row r="18" spans="3:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F18" s="155">
+      <c r="F18" s="159">
         <v>212</v>
       </c>
-      <c r="G18" s="155"/>
-      <c r="H18" s="155"/>
-      <c r="I18" s="155"/>
-      <c r="J18" s="155"/>
-      <c r="K18" s="155"/>
+      <c r="G18" s="159"/>
+      <c r="H18" s="159"/>
+      <c r="I18" s="159"/>
+      <c r="J18" s="159"/>
+      <c r="K18" s="159"/>
       <c r="M18" s="24"/>
       <c r="N18">
         <v>16</v>
@@ -9809,26 +10062,26 @@
         <f>1066*0.3+1066</f>
         <v>1385.8</v>
       </c>
-      <c r="Q18" s="157"/>
-      <c r="R18" s="158"/>
-      <c r="S18" s="159"/>
-      <c r="T18" s="160"/>
-      <c r="U18" s="150"/>
+      <c r="Q18" s="161"/>
+      <c r="R18" s="162"/>
+      <c r="S18" s="163"/>
+      <c r="T18" s="164"/>
+      <c r="U18" s="165"/>
       <c r="Y18">
         <f>Y17*Z5+Y17</f>
         <v>393.73763856992883</v>
       </c>
     </row>
     <row r="19" spans="3:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="155">
+      <c r="E19" s="159">
         <v>424</v>
       </c>
-      <c r="F19" s="155"/>
-      <c r="G19" s="155"/>
-      <c r="H19" s="155"/>
-      <c r="I19" s="155"/>
-      <c r="J19" s="155"/>
-      <c r="K19" s="155"/>
+      <c r="F19" s="159"/>
+      <c r="G19" s="159"/>
+      <c r="H19" s="159"/>
+      <c r="I19" s="159"/>
+      <c r="J19" s="159"/>
+      <c r="K19" s="159"/>
       <c r="M19" s="24"/>
       <c r="N19">
         <v>17</v>
@@ -9837,27 +10090,27 @@
         <f>1386*0.3+1386</f>
         <v>1801.8</v>
       </c>
-      <c r="Q19" s="157"/>
-      <c r="R19" s="158"/>
-      <c r="S19" s="159"/>
-      <c r="T19" s="160"/>
-      <c r="U19" s="150"/>
+      <c r="Q19" s="161"/>
+      <c r="R19" s="162"/>
+      <c r="S19" s="163"/>
+      <c r="T19" s="164"/>
+      <c r="U19" s="165"/>
       <c r="Y19">
         <f>Y18*Z5+Y18</f>
         <v>511.85893014090749</v>
       </c>
     </row>
     <row r="20" spans="3:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D20" s="155">
+      <c r="D20" s="159">
         <v>848</v>
       </c>
-      <c r="E20" s="155"/>
-      <c r="F20" s="155"/>
-      <c r="G20" s="155"/>
-      <c r="H20" s="155"/>
-      <c r="I20" s="155"/>
-      <c r="J20" s="155"/>
-      <c r="K20" s="155"/>
+      <c r="E20" s="159"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="159"/>
+      <c r="H20" s="159"/>
+      <c r="I20" s="159"/>
+      <c r="J20" s="159"/>
+      <c r="K20" s="159"/>
       <c r="M20" s="24"/>
       <c r="N20">
         <v>18</v>
@@ -9866,28 +10119,28 @@
         <f>1802*0.3+1802</f>
         <v>2342.6</v>
       </c>
-      <c r="Q20" s="157"/>
-      <c r="R20" s="158"/>
-      <c r="S20" s="159"/>
-      <c r="T20" s="160"/>
-      <c r="U20" s="150"/>
+      <c r="Q20" s="161"/>
+      <c r="R20" s="162"/>
+      <c r="S20" s="163"/>
+      <c r="T20" s="164"/>
+      <c r="U20" s="165"/>
       <c r="Y20">
         <f>Y19*Z5+Y19</f>
         <v>665.41660918317973</v>
       </c>
     </row>
     <row r="21" spans="3:25" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="155">
+      <c r="C21" s="159">
         <v>1654</v>
       </c>
-      <c r="D21" s="155"/>
-      <c r="E21" s="155"/>
-      <c r="F21" s="155"/>
-      <c r="G21" s="155"/>
-      <c r="H21" s="155"/>
-      <c r="I21" s="155"/>
-      <c r="J21" s="155"/>
-      <c r="K21" s="155"/>
+      <c r="D21" s="159"/>
+      <c r="E21" s="159"/>
+      <c r="F21" s="159"/>
+      <c r="G21" s="159"/>
+      <c r="H21" s="159"/>
+      <c r="I21" s="159"/>
+      <c r="J21" s="159"/>
+      <c r="K21" s="159"/>
       <c r="M21" s="24"/>
       <c r="N21">
         <v>19</v>
@@ -9896,11 +10149,11 @@
         <f>2342*0.3+2343</f>
         <v>3045.6</v>
       </c>
-      <c r="Q21" s="157"/>
-      <c r="R21" s="158"/>
-      <c r="S21" s="159"/>
-      <c r="T21" s="160"/>
-      <c r="U21" s="150"/>
+      <c r="Q21" s="161"/>
+      <c r="R21" s="162"/>
+      <c r="S21" s="163"/>
+      <c r="T21" s="164"/>
+      <c r="U21" s="165"/>
       <c r="Y21">
         <f>Y20*Z5+Y20</f>
         <v>865.04159193813371</v>
@@ -9924,11 +10177,11 @@
         <f>3045*0.3+3045</f>
         <v>3958.5</v>
       </c>
-      <c r="Q22" s="157"/>
-      <c r="R22" s="158"/>
-      <c r="S22" s="159"/>
-      <c r="T22" s="160"/>
-      <c r="U22" s="150"/>
+      <c r="Q22" s="161"/>
+      <c r="R22" s="162"/>
+      <c r="S22" s="163"/>
+      <c r="T22" s="164"/>
+      <c r="U22" s="165"/>
       <c r="Y22">
         <f>Y21*Z5+Y21</f>
         <v>1124.5540695195739</v>
@@ -9952,11 +10205,11 @@
         <f>3959*0.3+3959</f>
         <v>5146.7</v>
       </c>
-      <c r="Q23" s="157"/>
-      <c r="R23" s="158"/>
-      <c r="S23" s="159"/>
-      <c r="T23" s="160"/>
-      <c r="U23" s="150"/>
+      <c r="Q23" s="161"/>
+      <c r="R23" s="162"/>
+      <c r="S23" s="163"/>
+      <c r="T23" s="164"/>
+      <c r="U23" s="165"/>
       <c r="Y23">
         <f>Y22*Z5+Y22</f>
         <v>1461.920290375446</v>
@@ -9980,11 +10233,11 @@
         <f>5147*0.3+5147</f>
         <v>6691.1</v>
       </c>
-      <c r="Q24" s="157"/>
-      <c r="R24" s="158"/>
-      <c r="S24" s="159"/>
-      <c r="T24" s="160"/>
-      <c r="U24" s="150"/>
+      <c r="Q24" s="161"/>
+      <c r="R24" s="162"/>
+      <c r="S24" s="163"/>
+      <c r="T24" s="164"/>
+      <c r="U24" s="165"/>
       <c r="Y24">
         <f>Y23*Z5+Y23</f>
         <v>1900.4963774880798</v>
@@ -10008,11 +10261,11 @@
         <f>6691*0.3+6691</f>
         <v>8698.2999999999993</v>
       </c>
-      <c r="Q25" s="157"/>
-      <c r="R25" s="158"/>
-      <c r="S25" s="159"/>
-      <c r="T25" s="160"/>
-      <c r="U25" s="150"/>
+      <c r="Q25" s="161"/>
+      <c r="R25" s="162"/>
+      <c r="S25" s="163"/>
+      <c r="T25" s="164"/>
+      <c r="U25" s="165"/>
       <c r="Y25">
         <f>Y24*Z5+Y24</f>
         <v>2470.6452907345038</v>
@@ -10036,11 +10289,11 @@
         <f>8698*0.3+8698</f>
         <v>11307.4</v>
       </c>
-      <c r="Q26" s="157"/>
-      <c r="R26" s="158"/>
-      <c r="S26" s="159"/>
-      <c r="T26" s="160"/>
-      <c r="U26" s="150"/>
+      <c r="Q26" s="161"/>
+      <c r="R26" s="162"/>
+      <c r="S26" s="163"/>
+      <c r="T26" s="164"/>
+      <c r="U26" s="165"/>
       <c r="Y26">
         <f>Y25*Z5+Y25</f>
         <v>3211.838877954855</v>
@@ -10064,11 +10317,11 @@
         <f>11307*0.3+11307</f>
         <v>14699.1</v>
       </c>
-      <c r="Q27" s="157"/>
-      <c r="R27" s="158"/>
-      <c r="S27" s="159"/>
-      <c r="T27" s="160"/>
-      <c r="U27" s="150"/>
+      <c r="Q27" s="161"/>
+      <c r="R27" s="162"/>
+      <c r="S27" s="163"/>
+      <c r="T27" s="164"/>
+      <c r="U27" s="165"/>
       <c r="Y27">
         <f>Y26*Z5+Y26</f>
         <v>4175.3905413413113</v>
@@ -10092,11 +10345,11 @@
         <f>14699*0.3+14699</f>
         <v>19108.7</v>
       </c>
-      <c r="Q28" s="157"/>
-      <c r="R28" s="158"/>
-      <c r="S28" s="159"/>
-      <c r="T28" s="160"/>
-      <c r="U28" s="150"/>
+      <c r="Q28" s="161"/>
+      <c r="R28" s="162"/>
+      <c r="S28" s="163"/>
+      <c r="T28" s="164"/>
+      <c r="U28" s="165"/>
       <c r="Y28">
         <f>Y27*Z5+Y27</f>
         <v>5428.007703743705</v>
@@ -10120,11 +10373,11 @@
         <f>19109*0.3+19109</f>
         <v>24841.7</v>
       </c>
-      <c r="Q29" s="157"/>
-      <c r="R29" s="158"/>
-      <c r="S29" s="159"/>
-      <c r="T29" s="160"/>
-      <c r="U29" s="150"/>
+      <c r="Q29" s="161"/>
+      <c r="R29" s="162"/>
+      <c r="S29" s="163"/>
+      <c r="T29" s="164"/>
+      <c r="U29" s="165"/>
       <c r="Y29">
         <f>Y28*Z5+Y28</f>
         <v>7056.4100148668167</v>
@@ -10148,11 +10401,11 @@
         <f>24842*0.3+24842</f>
         <v>32294.6</v>
       </c>
-      <c r="Q30" s="157"/>
-      <c r="R30" s="158"/>
-      <c r="S30" s="159"/>
-      <c r="T30" s="160"/>
-      <c r="U30" s="150"/>
+      <c r="Q30" s="161"/>
+      <c r="R30" s="162"/>
+      <c r="S30" s="163"/>
+      <c r="T30" s="164"/>
+      <c r="U30" s="165"/>
       <c r="Y30">
         <f>Y29*Z5+Y29</f>
         <v>9173.3330193268612</v>
@@ -10176,11 +10429,11 @@
         <f>32295*0.3+32294</f>
         <v>41982.5</v>
       </c>
-      <c r="Q31" s="157"/>
-      <c r="R31" s="158"/>
-      <c r="S31" s="159"/>
-      <c r="T31" s="160"/>
-      <c r="U31" s="150"/>
+      <c r="Q31" s="161"/>
+      <c r="R31" s="162"/>
+      <c r="S31" s="163"/>
+      <c r="T31" s="164"/>
+      <c r="U31" s="165"/>
       <c r="Y31">
         <f>Y30*Z5+Y30</f>
         <v>11925.33292512492</v>
@@ -10204,11 +10457,11 @@
         <f>41983*0.3+41983</f>
         <v>54577.9</v>
       </c>
-      <c r="Q32" s="157"/>
-      <c r="R32" s="158"/>
-      <c r="S32" s="159"/>
-      <c r="T32" s="160"/>
-      <c r="U32" s="150"/>
+      <c r="Q32" s="161"/>
+      <c r="R32" s="162"/>
+      <c r="S32" s="163"/>
+      <c r="T32" s="164"/>
+      <c r="U32" s="165"/>
       <c r="Y32" s="26">
         <f>Y31*Z5+Y31</f>
         <v>15502.932802662395</v>
@@ -10232,11 +10485,11 @@
         <f>54578*0.3+54578</f>
         <v>70951.399999999994</v>
       </c>
-      <c r="Q33" s="157"/>
-      <c r="R33" s="158"/>
-      <c r="S33" s="159"/>
-      <c r="T33" s="160"/>
-      <c r="U33" s="150"/>
+      <c r="Q33" s="161"/>
+      <c r="R33" s="162"/>
+      <c r="S33" s="163"/>
+      <c r="T33" s="164"/>
+      <c r="U33" s="165"/>
       <c r="Y33">
         <f>Y32*Z5+Y32</f>
         <v>20153.812643461115</v>
@@ -10260,11 +10513,11 @@
         <f>70951*0.3+70951</f>
         <v>92236.3</v>
       </c>
-      <c r="Q34" s="157"/>
-      <c r="R34" s="158"/>
-      <c r="S34" s="159"/>
-      <c r="T34" s="160"/>
-      <c r="U34" s="150"/>
+      <c r="Q34" s="161"/>
+      <c r="R34" s="162"/>
+      <c r="S34" s="163"/>
+      <c r="T34" s="164"/>
+      <c r="U34" s="165"/>
       <c r="Y34">
         <f>Y33*Z5+Y33</f>
         <v>26199.956436499451</v>
@@ -10288,11 +10541,11 @@
         <f>92236*0.3+92236</f>
         <v>119906.8</v>
       </c>
-      <c r="Q35" s="157"/>
-      <c r="R35" s="158"/>
-      <c r="S35" s="159"/>
-      <c r="T35" s="160"/>
-      <c r="U35" s="150"/>
+      <c r="Q35" s="161"/>
+      <c r="R35" s="162"/>
+      <c r="S35" s="163"/>
+      <c r="T35" s="164"/>
+      <c r="U35" s="165"/>
       <c r="Y35">
         <f>Y34*Z5+Y34</f>
         <v>34059.94336744929</v>
@@ -10316,11 +10569,11 @@
         <f>119907*0.3+119907</f>
         <v>155879.1</v>
       </c>
-      <c r="Q36" s="157"/>
-      <c r="R36" s="158"/>
-      <c r="S36" s="159"/>
-      <c r="T36" s="160"/>
-      <c r="U36" s="150"/>
+      <c r="Q36" s="161"/>
+      <c r="R36" s="162"/>
+      <c r="S36" s="163"/>
+      <c r="T36" s="164"/>
+      <c r="U36" s="165"/>
       <c r="Y36">
         <f>Y35*Z5+Y35</f>
         <v>44277.926377684074</v>
@@ -10344,11 +10597,11 @@
         <f>155879*0.3+155879</f>
         <v>202642.7</v>
       </c>
-      <c r="Q37" s="157"/>
-      <c r="R37" s="158"/>
-      <c r="S37" s="159"/>
-      <c r="T37" s="160"/>
-      <c r="U37" s="150"/>
+      <c r="Q37" s="161"/>
+      <c r="R37" s="162"/>
+      <c r="S37" s="163"/>
+      <c r="T37" s="164"/>
+      <c r="U37" s="165"/>
       <c r="Y37">
         <f>Y36*Z5+Y36</f>
         <v>57561.304290989297</v>
@@ -10372,11 +10625,11 @@
         <f>202643*0.3+202643</f>
         <v>263435.90000000002</v>
       </c>
-      <c r="Q38" s="157"/>
-      <c r="R38" s="158"/>
-      <c r="S38" s="159"/>
-      <c r="T38" s="160"/>
-      <c r="U38" s="150"/>
+      <c r="Q38" s="161"/>
+      <c r="R38" s="162"/>
+      <c r="S38" s="163"/>
+      <c r="T38" s="164"/>
+      <c r="U38" s="165"/>
       <c r="Y38">
         <f>Y37*Z5+Y37</f>
         <v>74829.69557828609</v>
@@ -10400,11 +10653,11 @@
         <f>263436*0.3+263436</f>
         <v>342466.8</v>
       </c>
-      <c r="Q39" s="157"/>
-      <c r="R39" s="158"/>
-      <c r="S39" s="159"/>
-      <c r="T39" s="160"/>
-      <c r="U39" s="150"/>
+      <c r="Q39" s="161"/>
+      <c r="R39" s="162"/>
+      <c r="S39" s="163"/>
+      <c r="T39" s="164"/>
+      <c r="U39" s="165"/>
       <c r="Y39">
         <f>Y38*Z5+Y38</f>
         <v>97278.604251771918</v>
@@ -10428,11 +10681,11 @@
         <f>342466*0.3+342466</f>
         <v>445205.8</v>
       </c>
-      <c r="Q40" s="157"/>
-      <c r="R40" s="158"/>
-      <c r="S40" s="159"/>
-      <c r="T40" s="160"/>
-      <c r="U40" s="150"/>
+      <c r="Q40" s="161"/>
+      <c r="R40" s="162"/>
+      <c r="S40" s="163"/>
+      <c r="T40" s="164"/>
+      <c r="U40" s="165"/>
       <c r="Y40">
         <f>Y39*Z5+Y39</f>
         <v>126462.18552730349</v>
@@ -10456,10 +10709,10 @@
         <f>445206*0.3+445206</f>
         <v>578767.80000000005</v>
       </c>
-      <c r="Q41" s="157"/>
-      <c r="R41" s="158"/>
-      <c r="S41" s="159"/>
-      <c r="T41" s="160"/>
+      <c r="Q41" s="161"/>
+      <c r="R41" s="162"/>
+      <c r="S41" s="163"/>
+      <c r="T41" s="164"/>
       <c r="Y41">
         <f>Y40*Z5+Y40</f>
         <v>164400.84118549453</v>
@@ -10483,9 +10736,9 @@
         <f>578768*0.3+578768</f>
         <v>752398.4</v>
       </c>
-      <c r="Q42" s="157"/>
-      <c r="R42" s="158"/>
-      <c r="S42" s="159"/>
+      <c r="Q42" s="161"/>
+      <c r="R42" s="162"/>
+      <c r="S42" s="163"/>
       <c r="Y42">
         <f>Y41*Z5+Y41</f>
         <v>213721.09354114288</v>
@@ -10509,8 +10762,8 @@
         <f>752398*0.3+752398</f>
         <v>978117.4</v>
       </c>
-      <c r="Q43" s="157"/>
-      <c r="R43" s="158"/>
+      <c r="Q43" s="161"/>
+      <c r="R43" s="162"/>
       <c r="Y43">
         <f>Y42*Z5+Y42</f>
         <v>277837.42160348571</v>
@@ -10534,7 +10787,7 @@
         <f>978117*0.3+978117</f>
         <v>1271552.1000000001</v>
       </c>
-      <c r="Q44" s="157"/>
+      <c r="Q44" s="161"/>
       <c r="Y44">
         <f>Y43*Z5+Y43</f>
         <v>361188.64808453142</v>
@@ -10662,108 +10915,105 @@
       <c r="N54"/>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A56" s="156" t="s">
+      <c r="A56" s="160" t="s">
         <v>27</v>
       </c>
-      <c r="B56" s="156"/>
-      <c r="C56" s="156"/>
-      <c r="D56" s="156"/>
-      <c r="E56" s="156"/>
-      <c r="F56" s="156"/>
-      <c r="G56" s="156"/>
-      <c r="H56" s="156"/>
-      <c r="I56" s="156"/>
-      <c r="J56" s="156"/>
-      <c r="K56" s="156"/>
+      <c r="B56" s="160"/>
+      <c r="C56" s="160"/>
+      <c r="D56" s="160"/>
+      <c r="E56" s="160"/>
+      <c r="F56" s="160"/>
+      <c r="G56" s="160"/>
+      <c r="H56" s="160"/>
+      <c r="I56" s="160"/>
+      <c r="J56" s="160"/>
+      <c r="K56" s="160"/>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A57" s="156"/>
-      <c r="B57" s="156"/>
-      <c r="C57" s="156"/>
-      <c r="D57" s="156"/>
-      <c r="E57" s="156"/>
-      <c r="F57" s="156"/>
-      <c r="G57" s="156"/>
-      <c r="H57" s="156"/>
-      <c r="I57" s="156"/>
-      <c r="J57" s="156"/>
-      <c r="K57" s="156"/>
-      <c r="L57" s="154" t="s">
+      <c r="A57" s="160"/>
+      <c r="B57" s="160"/>
+      <c r="C57" s="160"/>
+      <c r="D57" s="160"/>
+      <c r="E57" s="160"/>
+      <c r="F57" s="160"/>
+      <c r="G57" s="160"/>
+      <c r="H57" s="160"/>
+      <c r="I57" s="160"/>
+      <c r="J57" s="160"/>
+      <c r="K57" s="160"/>
+      <c r="L57" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="M57" s="154"/>
-      <c r="N57" s="154"/>
-      <c r="O57" s="154"/>
-      <c r="P57" s="154"/>
-      <c r="Q57" s="154"/>
-      <c r="R57" s="154"/>
-      <c r="S57" s="154"/>
-      <c r="T57" s="154"/>
-      <c r="U57" s="154"/>
-      <c r="V57" s="154"/>
-      <c r="W57" s="154"/>
+      <c r="M57" s="158"/>
+      <c r="N57" s="158"/>
+      <c r="O57" s="158"/>
+      <c r="P57" s="158"/>
+      <c r="Q57" s="158"/>
+      <c r="R57" s="158"/>
+      <c r="S57" s="158"/>
+      <c r="T57" s="158"/>
+      <c r="U57" s="158"/>
+      <c r="V57" s="158"/>
+      <c r="W57" s="158"/>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A58" s="152" t="s">
+      <c r="A58" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="B58" s="152"/>
-      <c r="C58" s="152"/>
-      <c r="D58" s="152"/>
-      <c r="E58" s="152"/>
-      <c r="F58" s="152"/>
-      <c r="G58" s="152"/>
-      <c r="H58" s="152"/>
-      <c r="I58" s="152"/>
-      <c r="J58" s="152"/>
-      <c r="K58" s="152"/>
+      <c r="B58" s="156"/>
+      <c r="C58" s="156"/>
+      <c r="D58" s="156"/>
+      <c r="E58" s="156"/>
+      <c r="F58" s="156"/>
+      <c r="G58" s="156"/>
+      <c r="H58" s="156"/>
+      <c r="I58" s="156"/>
+      <c r="J58" s="156"/>
+      <c r="K58" s="156"/>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A59" s="152"/>
-      <c r="B59" s="152"/>
-      <c r="C59" s="152"/>
-      <c r="D59" s="152"/>
-      <c r="E59" s="152"/>
-      <c r="F59" s="152"/>
-      <c r="G59" s="152"/>
-      <c r="H59" s="152"/>
-      <c r="I59" s="152"/>
-      <c r="J59" s="152"/>
-      <c r="K59" s="152"/>
+      <c r="A59" s="156"/>
+      <c r="B59" s="156"/>
+      <c r="C59" s="156"/>
+      <c r="D59" s="156"/>
+      <c r="E59" s="156"/>
+      <c r="F59" s="156"/>
+      <c r="G59" s="156"/>
+      <c r="H59" s="156"/>
+      <c r="I59" s="156"/>
+      <c r="J59" s="156"/>
+      <c r="K59" s="156"/>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A60" s="153" t="s">
+      <c r="A60" s="157" t="s">
         <v>30</v>
       </c>
-      <c r="B60" s="153"/>
-      <c r="C60" s="153"/>
-      <c r="D60" s="153"/>
-      <c r="E60" s="153"/>
-      <c r="F60" s="153"/>
-      <c r="G60" s="153"/>
-      <c r="H60" s="153"/>
-      <c r="I60" s="153"/>
-      <c r="J60" s="153"/>
-      <c r="K60" s="153"/>
+      <c r="B60" s="157"/>
+      <c r="C60" s="157"/>
+      <c r="D60" s="157"/>
+      <c r="E60" s="157"/>
+      <c r="F60" s="157"/>
+      <c r="G60" s="157"/>
+      <c r="H60" s="157"/>
+      <c r="I60" s="157"/>
+      <c r="J60" s="157"/>
+      <c r="K60" s="157"/>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A61" s="153"/>
-      <c r="B61" s="153"/>
-      <c r="C61" s="153"/>
-      <c r="D61" s="153"/>
-      <c r="E61" s="153"/>
-      <c r="F61" s="153"/>
-      <c r="G61" s="153"/>
-      <c r="H61" s="153"/>
-      <c r="I61" s="153"/>
-      <c r="J61" s="153"/>
-      <c r="K61" s="153"/>
+      <c r="A61" s="157"/>
+      <c r="B61" s="157"/>
+      <c r="C61" s="157"/>
+      <c r="D61" s="157"/>
+      <c r="E61" s="157"/>
+      <c r="F61" s="157"/>
+      <c r="G61" s="157"/>
+      <c r="H61" s="157"/>
+      <c r="I61" s="157"/>
+      <c r="J61" s="157"/>
+      <c r="K61" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="R11:R43"/>
-    <mergeCell ref="S12:S42"/>
-    <mergeCell ref="T13:T41"/>
     <mergeCell ref="U14:U40"/>
     <mergeCell ref="O5:U6"/>
     <mergeCell ref="O7:U8"/>
@@ -10780,6 +11030,9 @@
     <mergeCell ref="E19:K19"/>
     <mergeCell ref="D20:K20"/>
     <mergeCell ref="Q10:Q44"/>
+    <mergeCell ref="R11:R43"/>
+    <mergeCell ref="S12:S42"/>
+    <mergeCell ref="T13:T41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10810,68 +11063,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="153" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="147"/>
-      <c r="P1" s="147"/>
-      <c r="Q1" s="147"/>
-      <c r="R1" s="147"/>
-      <c r="S1" s="147"/>
-      <c r="T1" s="147"/>
-      <c r="U1" s="147"/>
-      <c r="V1" s="147"/>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
+      <c r="P1" s="153"/>
+      <c r="Q1" s="153"/>
+      <c r="R1" s="153"/>
+      <c r="S1" s="153"/>
+      <c r="T1" s="153"/>
+      <c r="U1" s="153"/>
+      <c r="V1" s="153"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="153" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="163" t="s">
+      <c r="B2" s="153"/>
+      <c r="C2" s="169" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="164"/>
-      <c r="E2" s="147" t="s">
+      <c r="D2" s="170"/>
+      <c r="E2" s="153" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="147"/>
-      <c r="G2" s="163" t="s">
+      <c r="F2" s="153"/>
+      <c r="G2" s="169" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="164"/>
-      <c r="I2" s="165" t="s">
+      <c r="H2" s="170"/>
+      <c r="I2" s="171" t="s">
         <v>88</v>
       </c>
-      <c r="J2" s="165"/>
-      <c r="K2" s="163" t="s">
+      <c r="J2" s="171"/>
+      <c r="K2" s="169" t="s">
         <v>89</v>
       </c>
-      <c r="L2" s="164"/>
-      <c r="M2" s="147" t="s">
+      <c r="L2" s="170"/>
+      <c r="M2" s="153" t="s">
         <v>90</v>
       </c>
-      <c r="N2" s="147"/>
-      <c r="O2" s="163" t="s">
+      <c r="N2" s="153"/>
+      <c r="O2" s="169" t="s">
         <v>91</v>
       </c>
-      <c r="P2" s="164"/>
-      <c r="AG2" s="147" t="s">
+      <c r="P2" s="170"/>
+      <c r="AG2" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="AH2" s="147"/>
+      <c r="AH2" s="153"/>
     </row>
     <row r="3" spans="1:34" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="36" t="s">
@@ -11182,34 +11435,34 @@
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A16" s="147" t="s">
+      <c r="A16" s="153" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="147"/>
-      <c r="C16" s="166" t="s">
+      <c r="B16" s="153"/>
+      <c r="C16" s="172" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="166"/>
-      <c r="E16" s="147" t="s">
+      <c r="D16" s="172"/>
+      <c r="E16" s="153" t="s">
         <v>94</v>
       </c>
-      <c r="F16" s="147"/>
-      <c r="G16" s="166" t="s">
+      <c r="F16" s="153"/>
+      <c r="G16" s="172" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="166"/>
-      <c r="I16" s="147" t="s">
+      <c r="H16" s="172"/>
+      <c r="I16" s="153" t="s">
         <v>96</v>
       </c>
-      <c r="J16" s="147"/>
-      <c r="K16" s="147" t="s">
+      <c r="J16" s="153"/>
+      <c r="K16" s="153" t="s">
         <v>97</v>
       </c>
-      <c r="L16" s="147"/>
-      <c r="M16" s="147" t="s">
+      <c r="L16" s="153"/>
+      <c r="M16" s="153" t="s">
         <v>98</v>
       </c>
-      <c r="N16" s="147"/>
+      <c r="N16" s="153"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="55" t="s">
@@ -11259,22 +11512,22 @@
     </row>
     <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:8" s="63" customFormat="1" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="161" t="s">
+      <c r="A21" s="167" t="s">
         <v>160</v>
       </c>
-      <c r="B21" s="162"/>
-      <c r="C21" s="161" t="s">
+      <c r="B21" s="168"/>
+      <c r="C21" s="167" t="s">
         <v>161</v>
       </c>
-      <c r="D21" s="162"/>
-      <c r="E21" s="161" t="s">
+      <c r="D21" s="168"/>
+      <c r="E21" s="167" t="s">
         <v>162</v>
       </c>
-      <c r="F21" s="162"/>
-      <c r="G21" s="161" t="s">
+      <c r="F21" s="168"/>
+      <c r="G21" s="167" t="s">
         <v>165</v>
       </c>
-      <c r="H21" s="162"/>
+      <c r="H21" s="168"/>
     </row>
     <row r="22" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A22" s="55" t="s">
@@ -11385,77 +11638,77 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B1" s="147" t="s">
+      <c r="B1" s="153" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
     </row>
     <row r="2" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="B2" s="171" t="s">
+      <c r="B2" s="177" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
+      <c r="C2" s="177"/>
+      <c r="D2" s="177"/>
     </row>
     <row r="3" spans="2:22" ht="15.6" x14ac:dyDescent="0.35">
       <c r="B3" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="167">
+      <c r="C3" s="173">
         <v>2</v>
       </c>
-      <c r="D3" s="167"/>
-      <c r="E3" s="167"/>
-      <c r="F3" s="167"/>
-      <c r="G3" s="167"/>
-      <c r="H3" s="167"/>
-      <c r="I3" s="167"/>
-      <c r="J3" s="167"/>
-      <c r="K3" s="167"/>
-      <c r="L3" s="167"/>
-      <c r="M3" s="167"/>
-      <c r="N3" s="167"/>
-      <c r="O3" s="167"/>
-      <c r="P3" s="167"/>
-      <c r="Q3" s="167"/>
-      <c r="R3" s="167"/>
-      <c r="S3" s="167"/>
-      <c r="T3" s="167"/>
-      <c r="U3" s="167"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="173"/>
+      <c r="F3" s="173"/>
+      <c r="G3" s="173"/>
+      <c r="H3" s="173"/>
+      <c r="I3" s="173"/>
+      <c r="J3" s="173"/>
+      <c r="K3" s="173"/>
+      <c r="L3" s="173"/>
+      <c r="M3" s="173"/>
+      <c r="N3" s="173"/>
+      <c r="O3" s="173"/>
+      <c r="P3" s="173"/>
+      <c r="Q3" s="173"/>
+      <c r="R3" s="173"/>
+      <c r="S3" s="173"/>
+      <c r="T3" s="173"/>
+      <c r="U3" s="173"/>
     </row>
     <row r="4" spans="2:22" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="168" t="s">
+      <c r="B4" s="174" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="168"/>
-      <c r="D4" s="168"/>
-      <c r="E4" s="168"/>
-      <c r="F4" s="168"/>
-      <c r="G4" s="168"/>
-      <c r="H4" s="169"/>
-      <c r="I4" s="168" t="s">
+      <c r="C4" s="174"/>
+      <c r="D4" s="174"/>
+      <c r="E4" s="174"/>
+      <c r="F4" s="174"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="175"/>
+      <c r="I4" s="174" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="168"/>
-      <c r="K4" s="168"/>
-      <c r="L4" s="168"/>
-      <c r="M4" s="168"/>
-      <c r="N4" s="168"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="168" t="s">
+      <c r="J4" s="174"/>
+      <c r="K4" s="174"/>
+      <c r="L4" s="174"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="174"/>
+      <c r="O4" s="175"/>
+      <c r="P4" s="174" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="168"/>
-      <c r="R4" s="168"/>
-      <c r="S4" s="168"/>
-      <c r="T4" s="168"/>
-      <c r="U4" s="168"/>
-      <c r="V4" s="169"/>
+      <c r="Q4" s="174"/>
+      <c r="R4" s="174"/>
+      <c r="S4" s="174"/>
+      <c r="T4" s="174"/>
+      <c r="U4" s="174"/>
+      <c r="V4" s="175"/>
     </row>
     <row r="5" spans="2:22" s="23" customFormat="1" ht="11.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B5" s="34"/>
@@ -11484,56 +11737,56 @@
       <c r="B6" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="167">
+      <c r="C6" s="173">
         <v>4</v>
       </c>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="167"/>
-      <c r="H6" s="167"/>
-      <c r="I6" s="167"/>
-      <c r="J6" s="167"/>
-      <c r="K6" s="167"/>
-      <c r="L6" s="167"/>
-      <c r="M6" s="167"/>
-      <c r="N6" s="167"/>
-      <c r="O6" s="167"/>
-      <c r="P6" s="167"/>
-      <c r="Q6" s="167"/>
-      <c r="R6" s="167"/>
-      <c r="S6" s="167"/>
-      <c r="T6" s="167"/>
-      <c r="U6" s="167"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="173"/>
+      <c r="F6" s="173"/>
+      <c r="G6" s="173"/>
+      <c r="H6" s="173"/>
+      <c r="I6" s="173"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="173"/>
+      <c r="L6" s="173"/>
+      <c r="M6" s="173"/>
+      <c r="N6" s="173"/>
+      <c r="O6" s="173"/>
+      <c r="P6" s="173"/>
+      <c r="Q6" s="173"/>
+      <c r="R6" s="173"/>
+      <c r="S6" s="173"/>
+      <c r="T6" s="173"/>
+      <c r="U6" s="173"/>
     </row>
     <row r="7" spans="2:22" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="168" t="s">
+      <c r="B7" s="174" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="168"/>
-      <c r="D7" s="168"/>
-      <c r="E7" s="168"/>
-      <c r="F7" s="168"/>
-      <c r="G7" s="168"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="168" t="s">
+      <c r="C7" s="174"/>
+      <c r="D7" s="174"/>
+      <c r="E7" s="174"/>
+      <c r="F7" s="174"/>
+      <c r="G7" s="174"/>
+      <c r="H7" s="175"/>
+      <c r="I7" s="174" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="168"/>
-      <c r="K7" s="168"/>
-      <c r="L7" s="168"/>
-      <c r="M7" s="168"/>
-      <c r="N7" s="168"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="172" t="s">
+      <c r="J7" s="174"/>
+      <c r="K7" s="174"/>
+      <c r="L7" s="174"/>
+      <c r="M7" s="174"/>
+      <c r="N7" s="174"/>
+      <c r="O7" s="175"/>
+      <c r="P7" s="178" t="s">
         <v>45</v>
       </c>
-      <c r="Q7" s="172"/>
-      <c r="R7" s="172"/>
-      <c r="S7" s="172"/>
-      <c r="T7" s="172"/>
-      <c r="U7" s="172"/>
-      <c r="V7" s="173"/>
+      <c r="Q7" s="178"/>
+      <c r="R7" s="178"/>
+      <c r="S7" s="178"/>
+      <c r="T7" s="178"/>
+      <c r="U7" s="178"/>
+      <c r="V7" s="179"/>
     </row>
     <row r="8" spans="2:22" s="23" customFormat="1" ht="11.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B8" s="34"/>
@@ -11562,56 +11815,56 @@
       <c r="B9" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="167">
+      <c r="C9" s="173">
         <v>8</v>
       </c>
-      <c r="D9" s="167"/>
-      <c r="E9" s="167"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="167"/>
-      <c r="H9" s="167"/>
-      <c r="I9" s="167"/>
-      <c r="J9" s="167"/>
-      <c r="K9" s="167"/>
-      <c r="L9" s="167"/>
-      <c r="M9" s="167"/>
-      <c r="N9" s="167"/>
-      <c r="O9" s="167"/>
-      <c r="P9" s="167"/>
-      <c r="Q9" s="167"/>
-      <c r="R9" s="167"/>
-      <c r="S9" s="167"/>
-      <c r="T9" s="167"/>
-      <c r="U9" s="167"/>
+      <c r="D9" s="173"/>
+      <c r="E9" s="173"/>
+      <c r="F9" s="173"/>
+      <c r="G9" s="173"/>
+      <c r="H9" s="173"/>
+      <c r="I9" s="173"/>
+      <c r="J9" s="173"/>
+      <c r="K9" s="173"/>
+      <c r="L9" s="173"/>
+      <c r="M9" s="173"/>
+      <c r="N9" s="173"/>
+      <c r="O9" s="173"/>
+      <c r="P9" s="173"/>
+      <c r="Q9" s="173"/>
+      <c r="R9" s="173"/>
+      <c r="S9" s="173"/>
+      <c r="T9" s="173"/>
+      <c r="U9" s="173"/>
     </row>
     <row r="10" spans="2:22" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="168" t="s">
+      <c r="B10" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="168"/>
-      <c r="D10" s="168"/>
-      <c r="E10" s="168"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="168"/>
-      <c r="H10" s="169"/>
-      <c r="I10" s="168" t="s">
+      <c r="C10" s="174"/>
+      <c r="D10" s="174"/>
+      <c r="E10" s="174"/>
+      <c r="F10" s="174"/>
+      <c r="G10" s="174"/>
+      <c r="H10" s="175"/>
+      <c r="I10" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="168"/>
-      <c r="K10" s="168"/>
-      <c r="L10" s="168"/>
-      <c r="M10" s="168"/>
-      <c r="N10" s="168"/>
-      <c r="O10" s="169"/>
-      <c r="P10" s="168" t="s">
+      <c r="J10" s="174"/>
+      <c r="K10" s="174"/>
+      <c r="L10" s="174"/>
+      <c r="M10" s="174"/>
+      <c r="N10" s="174"/>
+      <c r="O10" s="175"/>
+      <c r="P10" s="174" t="s">
         <v>51</v>
       </c>
-      <c r="Q10" s="168"/>
-      <c r="R10" s="168"/>
-      <c r="S10" s="168"/>
-      <c r="T10" s="168"/>
-      <c r="U10" s="168"/>
-      <c r="V10" s="169"/>
+      <c r="Q10" s="174"/>
+      <c r="R10" s="174"/>
+      <c r="S10" s="174"/>
+      <c r="T10" s="174"/>
+      <c r="U10" s="174"/>
+      <c r="V10" s="175"/>
     </row>
     <row r="11" spans="2:22" s="23" customFormat="1" ht="11.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B11" s="34"/>
@@ -11640,56 +11893,56 @@
       <c r="B12" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="167">
+      <c r="C12" s="173">
         <v>16</v>
       </c>
-      <c r="D12" s="167"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="167"/>
-      <c r="H12" s="167"/>
-      <c r="I12" s="167"/>
-      <c r="J12" s="167"/>
-      <c r="K12" s="167"/>
-      <c r="L12" s="167"/>
-      <c r="M12" s="167"/>
-      <c r="N12" s="167"/>
-      <c r="O12" s="167"/>
-      <c r="P12" s="167"/>
-      <c r="Q12" s="167"/>
-      <c r="R12" s="167"/>
-      <c r="S12" s="167"/>
-      <c r="T12" s="167"/>
-      <c r="U12" s="167"/>
+      <c r="D12" s="173"/>
+      <c r="E12" s="173"/>
+      <c r="F12" s="173"/>
+      <c r="G12" s="173"/>
+      <c r="H12" s="173"/>
+      <c r="I12" s="173"/>
+      <c r="J12" s="173"/>
+      <c r="K12" s="173"/>
+      <c r="L12" s="173"/>
+      <c r="M12" s="173"/>
+      <c r="N12" s="173"/>
+      <c r="O12" s="173"/>
+      <c r="P12" s="173"/>
+      <c r="Q12" s="173"/>
+      <c r="R12" s="173"/>
+      <c r="S12" s="173"/>
+      <c r="T12" s="173"/>
+      <c r="U12" s="173"/>
     </row>
     <row r="13" spans="2:22" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="168" t="s">
+      <c r="B13" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="168"/>
-      <c r="D13" s="168"/>
-      <c r="E13" s="168"/>
-      <c r="F13" s="168"/>
-      <c r="G13" s="168"/>
-      <c r="H13" s="169"/>
-      <c r="I13" s="168" t="s">
+      <c r="C13" s="174"/>
+      <c r="D13" s="174"/>
+      <c r="E13" s="174"/>
+      <c r="F13" s="174"/>
+      <c r="G13" s="174"/>
+      <c r="H13" s="175"/>
+      <c r="I13" s="174" t="s">
         <v>49</v>
       </c>
-      <c r="J13" s="168"/>
-      <c r="K13" s="168"/>
-      <c r="L13" s="168"/>
-      <c r="M13" s="168"/>
-      <c r="N13" s="168"/>
-      <c r="O13" s="169"/>
-      <c r="P13" s="168" t="s">
+      <c r="J13" s="174"/>
+      <c r="K13" s="174"/>
+      <c r="L13" s="174"/>
+      <c r="M13" s="174"/>
+      <c r="N13" s="174"/>
+      <c r="O13" s="175"/>
+      <c r="P13" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="Q13" s="168"/>
-      <c r="R13" s="168"/>
-      <c r="S13" s="168"/>
-      <c r="T13" s="168"/>
-      <c r="U13" s="168"/>
-      <c r="V13" s="169"/>
+      <c r="Q13" s="174"/>
+      <c r="R13" s="174"/>
+      <c r="S13" s="174"/>
+      <c r="T13" s="174"/>
+      <c r="U13" s="174"/>
+      <c r="V13" s="175"/>
     </row>
     <row r="14" spans="2:22" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="17" spans="2:24" x14ac:dyDescent="0.3">
@@ -11705,30 +11958,30 @@
       <c r="E17" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="147" t="s">
+      <c r="F17" s="153" t="s">
         <v>58</v>
       </c>
-      <c r="G17" s="147"/>
+      <c r="G17" s="153"/>
       <c r="H17" t="s">
         <v>52</v>
       </c>
       <c r="I17" t="s">
         <v>53</v>
       </c>
-      <c r="J17" s="147" t="s">
+      <c r="J17" s="153" t="s">
         <v>56</v>
       </c>
-      <c r="K17" s="147"/>
+      <c r="K17" s="153"/>
       <c r="L17" t="s">
         <v>59</v>
       </c>
       <c r="M17" t="s">
         <v>54</v>
       </c>
-      <c r="N17" s="170" t="s">
+      <c r="N17" s="176" t="s">
         <v>55</v>
       </c>
-      <c r="O17" s="170"/>
+      <c r="O17" s="176"/>
       <c r="P17" t="s">
         <v>57</v>
       </c>
@@ -11755,56 +12008,56 @@
       <c r="B19" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="167">
+      <c r="C19" s="173">
         <v>2</v>
       </c>
-      <c r="D19" s="167"/>
-      <c r="E19" s="167"/>
-      <c r="F19" s="167"/>
-      <c r="G19" s="167"/>
-      <c r="H19" s="167"/>
-      <c r="I19" s="167"/>
-      <c r="J19" s="167"/>
-      <c r="K19" s="167"/>
-      <c r="L19" s="167"/>
-      <c r="M19" s="167"/>
-      <c r="N19" s="167"/>
-      <c r="O19" s="167"/>
-      <c r="P19" s="167"/>
-      <c r="Q19" s="167"/>
-      <c r="R19" s="167"/>
-      <c r="S19" s="167"/>
-      <c r="T19" s="167"/>
-      <c r="U19" s="167"/>
+      <c r="D19" s="173"/>
+      <c r="E19" s="173"/>
+      <c r="F19" s="173"/>
+      <c r="G19" s="173"/>
+      <c r="H19" s="173"/>
+      <c r="I19" s="173"/>
+      <c r="J19" s="173"/>
+      <c r="K19" s="173"/>
+      <c r="L19" s="173"/>
+      <c r="M19" s="173"/>
+      <c r="N19" s="173"/>
+      <c r="O19" s="173"/>
+      <c r="P19" s="173"/>
+      <c r="Q19" s="173"/>
+      <c r="R19" s="173"/>
+      <c r="S19" s="173"/>
+      <c r="T19" s="173"/>
+      <c r="U19" s="173"/>
     </row>
     <row r="20" spans="2:24" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="168" t="s">
+      <c r="B20" s="174" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="168"/>
-      <c r="D20" s="168"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="168"/>
-      <c r="H20" s="169"/>
-      <c r="I20" s="168" t="s">
+      <c r="C20" s="174"/>
+      <c r="D20" s="174"/>
+      <c r="E20" s="174"/>
+      <c r="F20" s="174"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="175"/>
+      <c r="I20" s="174" t="s">
         <v>71</v>
       </c>
-      <c r="J20" s="168"/>
-      <c r="K20" s="168"/>
-      <c r="L20" s="168"/>
-      <c r="M20" s="168"/>
-      <c r="N20" s="168"/>
-      <c r="O20" s="169"/>
-      <c r="P20" s="168" t="s">
+      <c r="J20" s="174"/>
+      <c r="K20" s="174"/>
+      <c r="L20" s="174"/>
+      <c r="M20" s="174"/>
+      <c r="N20" s="174"/>
+      <c r="O20" s="175"/>
+      <c r="P20" s="174" t="s">
         <v>70</v>
       </c>
-      <c r="Q20" s="168"/>
-      <c r="R20" s="168"/>
-      <c r="S20" s="168"/>
-      <c r="T20" s="168"/>
-      <c r="U20" s="168"/>
-      <c r="V20" s="169"/>
+      <c r="Q20" s="174"/>
+      <c r="R20" s="174"/>
+      <c r="S20" s="174"/>
+      <c r="T20" s="174"/>
+      <c r="U20" s="174"/>
+      <c r="V20" s="175"/>
     </row>
     <row r="21" spans="2:24" s="23" customFormat="1" ht="11.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B21" s="34"/>
@@ -11833,56 +12086,56 @@
       <c r="B22" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="167">
+      <c r="C22" s="173">
         <v>4</v>
       </c>
-      <c r="D22" s="167"/>
-      <c r="E22" s="167"/>
-      <c r="F22" s="167"/>
-      <c r="G22" s="167"/>
-      <c r="H22" s="167"/>
-      <c r="I22" s="167"/>
-      <c r="J22" s="167"/>
-      <c r="K22" s="167"/>
-      <c r="L22" s="167"/>
-      <c r="M22" s="167"/>
-      <c r="N22" s="167"/>
-      <c r="O22" s="167"/>
-      <c r="P22" s="167"/>
-      <c r="Q22" s="167"/>
-      <c r="R22" s="167"/>
-      <c r="S22" s="167"/>
-      <c r="T22" s="167"/>
-      <c r="U22" s="167"/>
+      <c r="D22" s="173"/>
+      <c r="E22" s="173"/>
+      <c r="F22" s="173"/>
+      <c r="G22" s="173"/>
+      <c r="H22" s="173"/>
+      <c r="I22" s="173"/>
+      <c r="J22" s="173"/>
+      <c r="K22" s="173"/>
+      <c r="L22" s="173"/>
+      <c r="M22" s="173"/>
+      <c r="N22" s="173"/>
+      <c r="O22" s="173"/>
+      <c r="P22" s="173"/>
+      <c r="Q22" s="173"/>
+      <c r="R22" s="173"/>
+      <c r="S22" s="173"/>
+      <c r="T22" s="173"/>
+      <c r="U22" s="173"/>
     </row>
     <row r="23" spans="2:24" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="168" t="s">
+      <c r="B23" s="174" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="168"/>
-      <c r="D23" s="168"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="168"/>
-      <c r="G23" s="168"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="168" t="s">
+      <c r="C23" s="174"/>
+      <c r="D23" s="174"/>
+      <c r="E23" s="174"/>
+      <c r="F23" s="174"/>
+      <c r="G23" s="174"/>
+      <c r="H23" s="175"/>
+      <c r="I23" s="174" t="s">
         <v>74</v>
       </c>
-      <c r="J23" s="168"/>
-      <c r="K23" s="168"/>
-      <c r="L23" s="168"/>
-      <c r="M23" s="168"/>
-      <c r="N23" s="168"/>
-      <c r="O23" s="169"/>
-      <c r="P23" s="168" t="s">
+      <c r="J23" s="174"/>
+      <c r="K23" s="174"/>
+      <c r="L23" s="174"/>
+      <c r="M23" s="174"/>
+      <c r="N23" s="174"/>
+      <c r="O23" s="175"/>
+      <c r="P23" s="174" t="s">
         <v>73</v>
       </c>
-      <c r="Q23" s="168"/>
-      <c r="R23" s="168"/>
-      <c r="S23" s="168"/>
-      <c r="T23" s="168"/>
-      <c r="U23" s="168"/>
-      <c r="V23" s="169"/>
+      <c r="Q23" s="174"/>
+      <c r="R23" s="174"/>
+      <c r="S23" s="174"/>
+      <c r="T23" s="174"/>
+      <c r="U23" s="174"/>
+      <c r="V23" s="175"/>
     </row>
     <row r="24" spans="2:24" s="23" customFormat="1" ht="11.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B24" s="34"/>
@@ -11911,56 +12164,56 @@
       <c r="B25" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="167">
+      <c r="C25" s="173">
         <v>8</v>
       </c>
-      <c r="D25" s="167"/>
-      <c r="E25" s="167"/>
-      <c r="F25" s="167"/>
-      <c r="G25" s="167"/>
-      <c r="H25" s="167"/>
-      <c r="I25" s="167"/>
-      <c r="J25" s="167"/>
-      <c r="K25" s="167"/>
-      <c r="L25" s="167"/>
-      <c r="M25" s="167"/>
-      <c r="N25" s="167"/>
-      <c r="O25" s="167"/>
-      <c r="P25" s="167"/>
-      <c r="Q25" s="167"/>
-      <c r="R25" s="167"/>
-      <c r="S25" s="167"/>
-      <c r="T25" s="167"/>
-      <c r="U25" s="167"/>
+      <c r="D25" s="173"/>
+      <c r="E25" s="173"/>
+      <c r="F25" s="173"/>
+      <c r="G25" s="173"/>
+      <c r="H25" s="173"/>
+      <c r="I25" s="173"/>
+      <c r="J25" s="173"/>
+      <c r="K25" s="173"/>
+      <c r="L25" s="173"/>
+      <c r="M25" s="173"/>
+      <c r="N25" s="173"/>
+      <c r="O25" s="173"/>
+      <c r="P25" s="173"/>
+      <c r="Q25" s="173"/>
+      <c r="R25" s="173"/>
+      <c r="S25" s="173"/>
+      <c r="T25" s="173"/>
+      <c r="U25" s="173"/>
     </row>
     <row r="26" spans="2:24" ht="43.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="168" t="s">
+      <c r="B26" s="174" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="168"/>
-      <c r="D26" s="168"/>
-      <c r="E26" s="168"/>
-      <c r="F26" s="168"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="168" t="s">
+      <c r="C26" s="174"/>
+      <c r="D26" s="174"/>
+      <c r="E26" s="174"/>
+      <c r="F26" s="174"/>
+      <c r="G26" s="174"/>
+      <c r="H26" s="175"/>
+      <c r="I26" s="174" t="s">
         <v>47</v>
       </c>
-      <c r="J26" s="168"/>
-      <c r="K26" s="168"/>
-      <c r="L26" s="168"/>
-      <c r="M26" s="168"/>
-      <c r="N26" s="168"/>
-      <c r="O26" s="169"/>
-      <c r="P26" s="168" t="s">
+      <c r="J26" s="174"/>
+      <c r="K26" s="174"/>
+      <c r="L26" s="174"/>
+      <c r="M26" s="174"/>
+      <c r="N26" s="174"/>
+      <c r="O26" s="175"/>
+      <c r="P26" s="174" t="s">
         <v>51</v>
       </c>
-      <c r="Q26" s="168"/>
-      <c r="R26" s="168"/>
-      <c r="S26" s="168"/>
-      <c r="T26" s="168"/>
-      <c r="U26" s="168"/>
-      <c r="V26" s="169"/>
+      <c r="Q26" s="174"/>
+      <c r="R26" s="174"/>
+      <c r="S26" s="174"/>
+      <c r="T26" s="174"/>
+      <c r="U26" s="174"/>
+      <c r="V26" s="175"/>
     </row>
     <row r="27" spans="2:24" s="23" customFormat="1" ht="11.4" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B27" s="34"/>
@@ -11989,56 +12242,56 @@
       <c r="B28" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="C28" s="167">
+      <c r="C28" s="173">
         <v>16</v>
       </c>
-      <c r="D28" s="167"/>
-      <c r="E28" s="167"/>
-      <c r="F28" s="167"/>
-      <c r="G28" s="167"/>
-      <c r="H28" s="167"/>
-      <c r="I28" s="167"/>
-      <c r="J28" s="167"/>
-      <c r="K28" s="167"/>
-      <c r="L28" s="167"/>
-      <c r="M28" s="167"/>
-      <c r="N28" s="167"/>
-      <c r="O28" s="167"/>
-      <c r="P28" s="167"/>
-      <c r="Q28" s="167"/>
-      <c r="R28" s="167"/>
-      <c r="S28" s="167"/>
-      <c r="T28" s="167"/>
-      <c r="U28" s="167"/>
+      <c r="D28" s="173"/>
+      <c r="E28" s="173"/>
+      <c r="F28" s="173"/>
+      <c r="G28" s="173"/>
+      <c r="H28" s="173"/>
+      <c r="I28" s="173"/>
+      <c r="J28" s="173"/>
+      <c r="K28" s="173"/>
+      <c r="L28" s="173"/>
+      <c r="M28" s="173"/>
+      <c r="N28" s="173"/>
+      <c r="O28" s="173"/>
+      <c r="P28" s="173"/>
+      <c r="Q28" s="173"/>
+      <c r="R28" s="173"/>
+      <c r="S28" s="173"/>
+      <c r="T28" s="173"/>
+      <c r="U28" s="173"/>
     </row>
     <row r="29" spans="2:24" ht="34.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="168" t="s">
+      <c r="B29" s="174" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="168"/>
-      <c r="D29" s="168"/>
-      <c r="E29" s="168"/>
-      <c r="F29" s="168"/>
-      <c r="G29" s="168"/>
-      <c r="H29" s="169"/>
-      <c r="I29" s="168" t="s">
+      <c r="C29" s="174"/>
+      <c r="D29" s="174"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="174"/>
+      <c r="G29" s="174"/>
+      <c r="H29" s="175"/>
+      <c r="I29" s="174" t="s">
         <v>49</v>
       </c>
-      <c r="J29" s="168"/>
-      <c r="K29" s="168"/>
-      <c r="L29" s="168"/>
-      <c r="M29" s="168"/>
-      <c r="N29" s="168"/>
-      <c r="O29" s="169"/>
-      <c r="P29" s="168" t="s">
+      <c r="J29" s="174"/>
+      <c r="K29" s="174"/>
+      <c r="L29" s="174"/>
+      <c r="M29" s="174"/>
+      <c r="N29" s="174"/>
+      <c r="O29" s="175"/>
+      <c r="P29" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="Q29" s="168"/>
-      <c r="R29" s="168"/>
-      <c r="S29" s="168"/>
-      <c r="T29" s="168"/>
-      <c r="U29" s="168"/>
-      <c r="V29" s="169"/>
+      <c r="Q29" s="174"/>
+      <c r="R29" s="174"/>
+      <c r="S29" s="174"/>
+      <c r="T29" s="174"/>
+      <c r="U29" s="174"/>
+      <c r="V29" s="175"/>
     </row>
     <row r="30" spans="2:24" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="2:24" x14ac:dyDescent="0.3">
@@ -12210,7 +12463,7 @@
     <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.44140625" customWidth="1"/>
     <col min="7" max="7" width="16.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.5546875" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.77734375" customWidth="1"/>
@@ -13155,19 +13408,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -13340,7 +13593,7 @@
       <c r="C32" t="s">
         <v>169</v>
       </c>
-      <c r="D32" s="174">
+      <c r="D32" s="180">
         <v>2</v>
       </c>
     </row>
@@ -13354,7 +13607,7 @@
       <c r="C33" t="s">
         <v>124</v>
       </c>
-      <c r="D33" s="148"/>
+      <c r="D33" s="154"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="68">
@@ -13366,7 +13619,7 @@
       <c r="C34" t="s">
         <v>236</v>
       </c>
-      <c r="D34" s="148"/>
+      <c r="D34" s="154"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="68">
@@ -13378,7 +13631,7 @@
       <c r="C35" t="s">
         <v>123</v>
       </c>
-      <c r="D35" s="148"/>
+      <c r="D35" s="154"/>
     </row>
     <row r="36" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="68">
@@ -13390,7 +13643,7 @@
       <c r="C36" t="s">
         <v>102</v>
       </c>
-      <c r="D36" s="148"/>
+      <c r="D36" s="154"/>
     </row>
     <row r="37" spans="1:4" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="78"/>
@@ -13408,7 +13661,7 @@
       <c r="C38" t="s">
         <v>169</v>
       </c>
-      <c r="D38" s="148">
+      <c r="D38" s="154">
         <v>2</v>
       </c>
     </row>
@@ -13422,7 +13675,7 @@
       <c r="C39" t="s">
         <v>176</v>
       </c>
-      <c r="D39" s="148"/>
+      <c r="D39" s="154"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="68">
@@ -13434,7 +13687,7 @@
       <c r="C40" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="148"/>
+      <c r="D40" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -14136,10 +14389,10 @@
       <c r="X8" s="93"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="175" t="s">
+      <c r="A9" s="181" t="s">
         <v>252</v>
       </c>
-      <c r="B9" s="176"/>
+      <c r="B9" s="182"/>
       <c r="C9" t="s">
         <v>262</v>
       </c>
@@ -14168,8 +14421,8 @@
       <c r="X9" s="93"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="177"/>
-      <c r="B10" s="178"/>
+      <c r="A10" s="183"/>
+      <c r="B10" s="184"/>
       <c r="C10" t="s">
         <v>263</v>
       </c>
@@ -14196,8 +14449,8 @@
       <c r="X10" s="93"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="177"/>
-      <c r="B11" s="178"/>
+      <c r="A11" s="183"/>
+      <c r="B11" s="184"/>
       <c r="C11" t="s">
         <v>248</v>
       </c>
@@ -14226,8 +14479,8 @@
       <c r="X11" s="93"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="177"/>
-      <c r="B12" s="178"/>
+      <c r="A12" s="183"/>
+      <c r="B12" s="184"/>
       <c r="C12" s="92" t="s">
         <v>250</v>
       </c>
@@ -14251,8 +14504,8 @@
       <c r="X12" s="93"/>
     </row>
     <row r="13" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="179"/>
-      <c r="B13" s="180"/>
+      <c r="A13" s="185"/>
+      <c r="B13" s="186"/>
       <c r="C13" t="s">
         <v>251</v>
       </c>
@@ -14280,10 +14533,10 @@
       <c r="W13" s="91"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="175" t="s">
+      <c r="A14" s="181" t="s">
         <v>247</v>
       </c>
-      <c r="B14" s="176"/>
+      <c r="B14" s="182"/>
       <c r="C14" t="s">
         <v>261</v>
       </c>
@@ -14311,8 +14564,8 @@
       <c r="W14" s="91"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="177"/>
-      <c r="B15" s="178"/>
+      <c r="A15" s="183"/>
+      <c r="B15" s="184"/>
       <c r="C15" t="s">
         <v>259</v>
       </c>
@@ -14340,8 +14593,8 @@
       <c r="W15" s="91"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="177"/>
-      <c r="B16" s="178"/>
+      <c r="A16" s="183"/>
+      <c r="B16" s="184"/>
       <c r="C16" t="s">
         <v>262</v>
       </c>
@@ -14373,8 +14626,8 @@
       <c r="W16" s="91"/>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" s="177"/>
-      <c r="B17" s="178"/>
+      <c r="A17" s="183"/>
+      <c r="B17" s="184"/>
       <c r="C17" s="95" t="s">
         <v>249</v>
       </c>
@@ -14406,8 +14659,8 @@
       <c r="W17" s="91"/>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A18" s="177"/>
-      <c r="B18" s="178"/>
+      <c r="A18" s="183"/>
+      <c r="B18" s="184"/>
       <c r="C18" s="92" t="s">
         <v>248</v>
       </c>
@@ -14441,8 +14694,8 @@
       <c r="W18" s="91"/>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" s="177"/>
-      <c r="B19" s="178"/>
+      <c r="A19" s="183"/>
+      <c r="B19" s="184"/>
       <c r="C19" s="92" t="s">
         <v>250</v>
       </c>
@@ -14474,8 +14727,8 @@
       <c r="W19" s="91"/>
     </row>
     <row r="20" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="179"/>
-      <c r="B20" s="180"/>
+      <c r="A20" s="185"/>
+      <c r="B20" s="186"/>
       <c r="C20" s="92" t="s">
         <v>251</v>
       </c>
@@ -14507,10 +14760,10 @@
       <c r="W20" s="91"/>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A21" s="175" t="s">
+      <c r="A21" s="181" t="s">
         <v>254</v>
       </c>
-      <c r="B21" s="176"/>
+      <c r="B21" s="182"/>
       <c r="C21" s="89" t="s">
         <v>249</v>
       </c>
@@ -14540,8 +14793,8 @@
       <c r="W21" s="91"/>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" s="177"/>
-      <c r="B22" s="178"/>
+      <c r="A22" s="183"/>
+      <c r="B22" s="184"/>
       <c r="C22" s="92" t="s">
         <v>248</v>
       </c>
@@ -14575,8 +14828,8 @@
       <c r="W22" s="91"/>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" s="177"/>
-      <c r="B23" s="178"/>
+      <c r="A23" s="183"/>
+      <c r="B23" s="184"/>
       <c r="C23" s="92" t="s">
         <v>250</v>
       </c>
@@ -14606,8 +14859,8 @@
       <c r="W23" s="91"/>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A24" s="177"/>
-      <c r="B24" s="178"/>
+      <c r="A24" s="183"/>
+      <c r="B24" s="184"/>
       <c r="C24" s="92" t="s">
         <v>251</v>
       </c>
@@ -14639,8 +14892,8 @@
       <c r="W24" s="91"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A25" s="177"/>
-      <c r="B25" s="178"/>
+      <c r="A25" s="183"/>
+      <c r="B25" s="184"/>
       <c r="C25" t="s">
         <v>261</v>
       </c>
@@ -14670,8 +14923,8 @@
       <c r="W25" s="91"/>
     </row>
     <row r="26" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="179"/>
-      <c r="B26" s="180"/>
+      <c r="A26" s="185"/>
+      <c r="B26" s="186"/>
       <c r="C26" t="s">
         <v>259</v>
       </c>
@@ -14699,10 +14952,10 @@
       <c r="W26" s="91"/>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A27" s="175" t="s">
+      <c r="A27" s="181" t="s">
         <v>255</v>
       </c>
-      <c r="B27" s="176"/>
+      <c r="B27" s="182"/>
       <c r="C27" s="92" t="s">
         <v>248</v>
       </c>
@@ -14730,8 +14983,8 @@
       <c r="W27" s="91"/>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A28" s="177"/>
-      <c r="B28" s="178"/>
+      <c r="A28" s="183"/>
+      <c r="B28" s="184"/>
       <c r="C28" s="89" t="s">
         <v>249</v>
       </c>
@@ -14759,8 +15012,8 @@
       <c r="W28" s="91"/>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A29" s="177"/>
-      <c r="B29" s="178"/>
+      <c r="A29" s="183"/>
+      <c r="B29" s="184"/>
       <c r="D29" s="91"/>
       <c r="E29" s="91"/>
       <c r="F29" s="91"/>
@@ -14783,8 +15036,8 @@
       <c r="W29" s="91"/>
     </row>
     <row r="30" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="179"/>
-      <c r="B30" s="180"/>
+      <c r="A30" s="185"/>
+      <c r="B30" s="186"/>
       <c r="D30" s="91"/>
       <c r="E30" s="91"/>
       <c r="F30" s="91"/>
